--- a/tests/fixtures/excel/duplicates_removed.xlsx
+++ b/tests/fixtures/excel/duplicates_removed.xlsx
@@ -3,9 +3,9 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
   <workbookPr filterPrivacy="1" codeName="ThisWorkbook" defaultThemeVersion="202300"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{9F61ED67-0959-4ABF-A0A1-D44933A85576}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{E94E106D-8AC9-4BA9-AC98-4E7DDF2EF1B3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="51420" windowHeight="21100" xr2:uid="{47469D64-3CED-4F43-91F1-E02A189032DD}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="10800" windowHeight="19485" xr2:uid="{D3BBCE71-D6E5-4977-A5E6-B071EBD0A9FA}"/>
   </bookViews>
   <sheets>
     <sheet name="Pairs" sheetId="1" r:id="rId1"/>
@@ -23,7 +23,32 @@
     <sheet name="TotalAway" sheetId="13" r:id="rId13"/>
     <sheet name="NotTotal" sheetId="14" r:id="rId14"/>
     <sheet name="EmptyBelow" sheetId="15" r:id="rId15"/>
+    <sheet name="Table" sheetId="16" r:id="rId16"/>
+    <sheet name="TableTotals" sheetId="17" r:id="rId17"/>
+    <sheet name="TableTotalsShapes" sheetId="18" r:id="rId18"/>
+    <sheet name="Reader" sheetId="19" r:id="rId19"/>
+    <sheet name="TableInner" sheetId="20" r:id="rId20"/>
+    <sheet name="TableCell" sheetId="21" r:id="rId21"/>
+    <sheet name="TableNoHeaderAsked" sheetId="22" r:id="rId22"/>
+    <sheet name="TableTotalsRow" sheetId="23" r:id="rId23"/>
+    <sheet name="TableCalc" sheetId="24" r:id="rId24"/>
+    <sheet name="TableHidden" sheetId="25" r:id="rId25"/>
+    <sheet name="TableFiltered" sheetId="26" r:id="rId26"/>
+    <sheet name="TableFilteredTotals" sheetId="27" r:id="rId27"/>
+    <sheet name="TableHeadless" sheetId="28" r:id="rId28"/>
+    <sheet name="TableEmptyRows" sheetId="29" r:id="rId29"/>
+    <sheet name="TableLastSum" sheetId="30" r:id="rId30"/>
+    <sheet name="TableSorted" sheetId="31" r:id="rId31"/>
+    <sheet name="TableUnique" sheetId="32" r:id="rId32"/>
+    <sheet name="TableWider" sheetId="33" r:id="rId33"/>
+    <sheet name="TableLonger" sheetId="34" r:id="rId34"/>
   </sheets>
+  <definedNames>
+    <definedName name="TableGone">Table!$B$7</definedName>
+    <definedName name="TableSpan">Table!$B$2:$B$5</definedName>
+    <definedName name="TotalsCell">TableTotals!$B$6</definedName>
+    <definedName name="TotalsSpan">TableTotals!$B$2:$B$5</definedName>
+  </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
@@ -53,7 +78,7 @@
     <author>Author</author>
   </authors>
   <commentList>
-    <comment ref="C3" authorId="0" shapeId="0" xr:uid="{3F8E066C-0E22-4AF5-8356-9B4451161A14}">
+    <comment ref="C3" authorId="0" shapeId="0" xr:uid="{16E0C017-8101-4864-A8E4-7236265D7EBE}">
       <text>
         <r>
           <rPr>
@@ -66,7 +91,92 @@
         </r>
       </text>
     </comment>
-    <comment ref="C7" authorId="0" shapeId="0" xr:uid="{660DE8FE-547C-45D3-888B-8CA4CF5A5A67}">
+    <comment ref="C7" authorId="0" shapeId="0" xr:uid="{F2B18077-D553-4306-B16F-7A2E727DF86F}">
+      <text>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <charset val="1"/>
+          </rPr>
+          <t>note on a removed row</t>
+        </r>
+      </text>
+    </comment>
+  </commentList>
+</comments>
+</file>
+
+<file path=xl/comments2.xml><?xml version="1.0" encoding="utf-8"?>
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr">
+  <authors>
+    <author>Author</author>
+  </authors>
+  <commentList>
+    <comment ref="C5" authorId="0" shapeId="0" xr:uid="{CCC7FD97-5C3E-4548-957E-0ACB188E042C}">
+      <text>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <charset val="1"/>
+          </rPr>
+          <t>note on a row that moves</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="C6" authorId="0" shapeId="0" xr:uid="{49F013B4-B8F0-444C-9C1B-55A903E8A28F}">
+      <text>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <charset val="1"/>
+          </rPr>
+          <t>note on a removed row</t>
+        </r>
+      </text>
+    </comment>
+  </commentList>
+</comments>
+</file>
+
+<file path=xl/comments3.xml><?xml version="1.0" encoding="utf-8"?>
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr">
+  <authors>
+    <author>Author</author>
+  </authors>
+  <commentList>
+    <comment ref="C5" authorId="0" shapeId="0" xr:uid="{C2E49B63-3AC8-42E6-A685-50C0227F95BA}">
+      <text>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <charset val="1"/>
+          </rPr>
+          <t>note on a row that moves</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="C6" authorId="0" shapeId="0" xr:uid="{8E7C52AB-F48A-4266-BEEB-D34FCED29FD1}">
+      <text>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <charset val="1"/>
+          </rPr>
+          <t>note on the totals row</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="C7" authorId="0" shapeId="0" xr:uid="{72257964-ABC5-4224-8E2A-44302256924F}">
       <text>
         <r>
           <rPr>
@@ -84,7 +194,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="495" uniqueCount="87">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="844" uniqueCount="94">
   <si>
     <t>v</t>
   </si>
@@ -341,23 +451,45 @@
     <t>m2</t>
   </si>
   <si>
+    <t>m3</t>
+  </si>
+  <si>
     <t>m4</t>
   </si>
   <si>
+    <t>m5</t>
+  </si>
+  <si>
     <t>m6</t>
+  </si>
+  <si>
+    <t>m7</t>
+  </si>
+  <si>
+    <t>o7</t>
+  </si>
+  <si>
+    <t>below</t>
+  </si>
+  <si>
+    <t>Total</t>
+  </si>
+  <si>
+    <t>calc</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="6">
+  <numFmts count="7">
     <numFmt numFmtId="164" formatCode="0.0"/>
     <numFmt numFmtId="165" formatCode="0.0%"/>
     <numFmt numFmtId="166" formatCode="0;0"/>
     <numFmt numFmtId="167" formatCode="&quot;a&quot;0"/>
     <numFmt numFmtId="169" formatCode="@&quot;!&quot;"/>
     <numFmt numFmtId="170" formatCode="@&quot; &quot;"/>
+    <numFmt numFmtId="171" formatCode="0.000"/>
   </numFmts>
   <fonts count="3" x14ac:knownFonts="1">
     <font>
@@ -382,7 +514,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="6">
+  <fills count="8">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -413,6 +545,18 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF00C800"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF0000C8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="1">
     <border>
@@ -427,7 +571,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="23">
+  <cellXfs count="26">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
@@ -451,12 +595,19 @@
     <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="171" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="0"/>
+  <dxfs count="1">
+    <dxf>
+      <numFmt numFmtId="164" formatCode="0.0"/>
+    </dxf>
+  </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
@@ -467,6 +618,561 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/charts/chart1.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+  <c:date1904 val="0"/>
+  <c:lang val="en-US"/>
+  <c:roundedCorners val="0"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
+      <c14:style val="102"/>
+    </mc:Choice>
+    <mc:Fallback>
+      <c:style val="2"/>
+    </mc:Fallback>
+  </mc:AlternateContent>
+  <c:chart>
+    <c:autoTitleDeleted val="0"/>
+    <c:plotArea>
+      <c:layout/>
+      <c:barChart>
+        <c:barDir val="col"/>
+        <c:grouping val="clustered"/>
+        <c:varyColors val="0"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:invertIfNegative val="0"/>
+          <c:val>
+            <c:numRef>
+              <c:f>Table!$B$2:$B$5</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="4"/>
+                <c:pt idx="0">
+                  <c:v>1</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>3</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>5</c:v>
+                </c:pt>
+                <c:pt idx="3" formatCode="0.000">
+                  <c:v>7</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000002-E14C-41E3-9A99-7A245F9399DC}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:dLbls>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+        </c:dLbls>
+        <c:gapWidth val="150"/>
+        <c:axId val="263180832"/>
+        <c:axId val="1166427791"/>
+      </c:barChart>
+      <c:catAx>
+        <c:axId val="263180832"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="b"/>
+        <c:majorTickMark val="out"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:crossAx val="1166427791"/>
+        <c:crosses val="autoZero"/>
+        <c:auto val="1"/>
+        <c:lblAlgn val="ctr"/>
+        <c:lblOffset val="100"/>
+        <c:noMultiLvlLbl val="0"/>
+      </c:catAx>
+      <c:valAx>
+        <c:axId val="1166427791"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="l"/>
+        <c:majorGridlines/>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="out"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:crossAx val="263180832"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="between"/>
+      </c:valAx>
+    </c:plotArea>
+    <c:legend>
+      <c:legendPos val="r"/>
+      <c:overlay val="0"/>
+    </c:legend>
+    <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
+    <c:extLst>
+      <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
+        <c16r3:dataDisplayOptions16>
+          <c16r3:dispNaAsBlank val="1"/>
+        </c16r3:dataDisplayOptions16>
+      </c:ext>
+    </c:extLst>
+  </c:chart>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
+    <c:pageSetup/>
+  </c:printSettings>
+</c:chartSpace>
+</file>
+
+<file path=xl/charts/chart2.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+  <c:date1904 val="0"/>
+  <c:lang val="en-US"/>
+  <c:roundedCorners val="0"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
+      <c14:style val="102"/>
+    </mc:Choice>
+    <mc:Fallback>
+      <c:style val="2"/>
+    </mc:Fallback>
+  </mc:AlternateContent>
+  <c:chart>
+    <c:autoTitleDeleted val="0"/>
+    <c:plotArea>
+      <c:layout/>
+      <c:barChart>
+        <c:barDir val="col"/>
+        <c:grouping val="clustered"/>
+        <c:varyColors val="0"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:invertIfNegative val="0"/>
+          <c:val>
+            <c:numRef>
+              <c:f>TableTotals!$B$2:$B$5</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="4"/>
+                <c:pt idx="0">
+                  <c:v>1</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>3</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>5</c:v>
+                </c:pt>
+                <c:pt idx="3" formatCode="0.000">
+                  <c:v>7</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000002-9D81-4C5C-9897-9B6D7F90E4DD}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:dLbls>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+        </c:dLbls>
+        <c:gapWidth val="150"/>
+        <c:axId val="263186864"/>
+        <c:axId val="1166366831"/>
+      </c:barChart>
+      <c:catAx>
+        <c:axId val="263186864"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="b"/>
+        <c:majorTickMark val="out"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:crossAx val="1166366831"/>
+        <c:crosses val="autoZero"/>
+        <c:auto val="1"/>
+        <c:lblAlgn val="ctr"/>
+        <c:lblOffset val="100"/>
+        <c:noMultiLvlLbl val="0"/>
+      </c:catAx>
+      <c:valAx>
+        <c:axId val="1166366831"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="l"/>
+        <c:majorGridlines/>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="out"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:crossAx val="263186864"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="between"/>
+      </c:valAx>
+    </c:plotArea>
+    <c:legend>
+      <c:legendPos val="r"/>
+      <c:overlay val="0"/>
+    </c:legend>
+    <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
+    <c:extLst>
+      <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
+        <c16r3:dataDisplayOptions16>
+          <c16r3:dispNaAsBlank val="1"/>
+        </c16r3:dataDisplayOptions16>
+      </c:ext>
+    </c:extLst>
+  </c:chart>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
+    <c:pageSetup/>
+  </c:printSettings>
+</c:chartSpace>
+</file>
+
+<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>457200</xdr:colOff>
+      <xdr:row>0</xdr:row>
+      <xdr:rowOff>127000</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>12</xdr:col>
+      <xdr:colOff>558800</xdr:colOff>
+      <xdr:row>8</xdr:row>
+      <xdr:rowOff>127000</xdr:rowOff>
+    </xdr:to>
+    <xdr:graphicFrame macro="">
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="2" name="Chart 1">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{3D69A4C1-A717-10EA-3F09-E859460C0E0F}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvGraphicFramePr/>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="0" y="0"/>
+        <a:ext cx="0" cy="0"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/drawings/drawing2.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>457200</xdr:colOff>
+      <xdr:row>0</xdr:row>
+      <xdr:rowOff>127000</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>12</xdr:col>
+      <xdr:colOff>558800</xdr:colOff>
+      <xdr:row>8</xdr:row>
+      <xdr:rowOff>127000</xdr:rowOff>
+    </xdr:to>
+    <xdr:graphicFrame macro="">
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="2" name="Chart 1">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{286A5A7F-3499-9C54-4A64-2AAC8E8F9710}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvGraphicFramePr/>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="0" y="0"/>
+        <a:ext cx="0" cy="0"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{0D4882FE-F6E2-4C03-A59F-F39B43E2AEC3}" name="TTable" displayName="TTable" ref="A1:C5" totalsRowShown="0">
+  <autoFilter ref="A1:C5" xr:uid="{0D4882FE-F6E2-4C03-A59F-F39B43E2AEC3}"/>
+  <tableColumns count="3">
+    <tableColumn id="1" xr3:uid="{14846AB2-7935-42AB-802F-B7D951A37403}" name="k"/>
+    <tableColumn id="2" xr3:uid="{5F12AF86-3951-4C30-BA55-3DB5BC5F4EB3}" name="n"/>
+    <tableColumn id="3" xr3:uid="{91D890C2-3C82-489F-85F1-0DF03534010D}" name="m"/>
+  </tableColumns>
+  <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+</table>
+</file>
+
+<file path=xl/tables/table10.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="10" xr:uid="{C230B1EA-E86B-45FD-B641-35FB30CE2BD9}" name="TTableFiltered" displayName="TTableFiltered" ref="A1:C5" totalsRowShown="0">
+  <autoFilter ref="A1:C5" xr:uid="{C230B1EA-E86B-45FD-B641-35FB30CE2BD9}">
+    <filterColumn colId="1">
+      <customFilters>
+        <customFilter operator="greaterThan" val="3"/>
+      </customFilters>
+    </filterColumn>
+  </autoFilter>
+  <tableColumns count="3">
+    <tableColumn id="1" xr3:uid="{044C36D7-BE2F-4900-B637-7ACD15CBAEE7}" name="k"/>
+    <tableColumn id="2" xr3:uid="{31E68E55-E858-4CA0-9EC5-A885437A7E23}" name="n"/>
+    <tableColumn id="3" xr3:uid="{B18428E6-873A-4948-BC50-1C3132B0082C}" name="m"/>
+  </tableColumns>
+  <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+</table>
+</file>
+
+<file path=xl/tables/table11.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="11" xr:uid="{B638A1BF-7CA9-4A50-9AA7-1B6745791F92}" name="TTableFilteredTotals" displayName="TTableFilteredTotals" ref="A1:C9" totalsRowCount="1">
+  <autoFilter ref="A1:C8" xr:uid="{B638A1BF-7CA9-4A50-9AA7-1B6745791F92}">
+    <filterColumn colId="1">
+      <customFilters>
+        <customFilter operator="lessThan" val="5"/>
+      </customFilters>
+    </filterColumn>
+  </autoFilter>
+  <tableColumns count="3">
+    <tableColumn id="1" xr3:uid="{A61CA155-CEE1-4586-BED5-009B6666C82C}" name="k" totalsRowLabel="Total"/>
+    <tableColumn id="2" xr3:uid="{78EFE0DD-F1C0-4C2F-B786-4E1133E8F6E1}" name="n" totalsRowFunction="sum"/>
+    <tableColumn id="3" xr3:uid="{51169B0A-37CE-4B77-9B78-CEB08BB3559D}" name="m" totalsRowFunction="count"/>
+  </tableColumns>
+  <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+</table>
+</file>
+
+<file path=xl/tables/table12.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="12" xr:uid="{3393723A-F810-45FB-B026-2477823A4609}" name="TTableHeadless" displayName="TTableHeadless" ref="A2:C5" headerRowCount="0" totalsRowShown="0">
+  <tableColumns count="3">
+    <tableColumn id="1" xr3:uid="{23BDCF90-B04E-4659-8DCB-DD8FFCE521F2}" name="k"/>
+    <tableColumn id="2" xr3:uid="{DF47EBCB-5A44-41D2-A8DD-B1256DBB2C18}" name="n"/>
+    <tableColumn id="3" xr3:uid="{1EAABF36-9F7F-4BAD-A826-952DD8E0712B}" name="m"/>
+  </tableColumns>
+  <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+</table>
+</file>
+
+<file path=xl/tables/table13.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="13" xr:uid="{C52AAB8F-0A42-477C-8869-7ACD616D66EF}" name="TTableEmptyRows" displayName="TTableEmptyRows" ref="A1:B4" totalsRowShown="0">
+  <autoFilter ref="A1:B4" xr:uid="{C52AAB8F-0A42-477C-8869-7ACD616D66EF}"/>
+  <tableColumns count="2">
+    <tableColumn id="1" xr3:uid="{7443699A-661A-4139-8D26-905B3ED206DF}" name="k"/>
+    <tableColumn id="2" xr3:uid="{CF1A8001-9F01-4440-AA99-41D44A914C53}" name="n"/>
+  </tableColumns>
+  <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+</table>
+</file>
+
+<file path=xl/tables/table14.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="14" xr:uid="{FE2BC8BA-B9A3-41A0-A393-73E84365FE91}" name="TTableLastSum" displayName="TTableLastSum" ref="A1:B5" totalsRowShown="0">
+  <autoFilter ref="A1:B5" xr:uid="{FE2BC8BA-B9A3-41A0-A393-73E84365FE91}"/>
+  <tableColumns count="2">
+    <tableColumn id="1" xr3:uid="{80727EBE-E3CB-440D-921B-171860C7DB61}" name="k"/>
+    <tableColumn id="2" xr3:uid="{D0C1C78E-8539-4D49-846B-5AD3DE0CD425}" name="n"/>
+  </tableColumns>
+  <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+</table>
+</file>
+
+<file path=xl/tables/table15.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="15" xr:uid="{F56B9058-3116-4203-A852-6EC64ED335AB}" name="TTableSorted" displayName="TTableSorted" ref="A1:C5" totalsRowShown="0">
+  <autoFilter ref="A1:C5" xr:uid="{F56B9058-3116-4203-A852-6EC64ED335AB}"/>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:C5">
+    <sortCondition ref="B2:B8"/>
+  </sortState>
+  <tableColumns count="3">
+    <tableColumn id="1" xr3:uid="{4BD27648-722F-4515-AC0A-21279742B5B4}" name="k"/>
+    <tableColumn id="2" xr3:uid="{F3A6244D-BB0C-41A7-8FAE-FDD3D226FE65}" name="n"/>
+    <tableColumn id="3" xr3:uid="{40950144-E418-4116-93FA-6FF37CE19CFA}" name="m"/>
+  </tableColumns>
+  <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+</table>
+</file>
+
+<file path=xl/tables/table16.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="16" xr:uid="{2E46C86D-4D70-408F-9049-C9BC71A45389}" name="TTableUnique" displayName="TTableUnique" ref="A1:C8" totalsRowShown="0">
+  <autoFilter ref="A1:C8" xr:uid="{2E46C86D-4D70-408F-9049-C9BC71A45389}"/>
+  <tableColumns count="3">
+    <tableColumn id="1" xr3:uid="{C2693D60-14D8-4A9A-9D81-CDD1F1ADAB7B}" name="k"/>
+    <tableColumn id="2" xr3:uid="{977EB0D5-E29E-4A31-8661-D9F7A8B6225B}" name="n"/>
+    <tableColumn id="3" xr3:uid="{6549EBCB-D598-4D0E-AEC9-5A285A4ADBC2}" name="m"/>
+  </tableColumns>
+  <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+</table>
+</file>
+
+<file path=xl/tables/table17.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="17" xr:uid="{B55ABC69-ABBE-4DA1-86FD-DE83274949CB}" name="TTableWider" displayName="TTableWider" ref="A1:C8" totalsRowShown="0">
+  <autoFilter ref="A1:C8" xr:uid="{B55ABC69-ABBE-4DA1-86FD-DE83274949CB}"/>
+  <tableColumns count="3">
+    <tableColumn id="1" xr3:uid="{A6D1D420-BBDE-4766-B550-FC22A11E3208}" name="k"/>
+    <tableColumn id="2" xr3:uid="{319DE8A6-262F-4C5A-A1B4-16DA1B56BD19}" name="n"/>
+    <tableColumn id="3" xr3:uid="{9DB3B652-5F2C-4EC1-B367-7A5F431AA75D}" name="m"/>
+  </tableColumns>
+  <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+</table>
+</file>
+
+<file path=xl/tables/table18.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="18" xr:uid="{BA93B42F-9927-452E-9F15-AB8EAAC0F454}" name="TTableLonger" displayName="TTableLonger" ref="A1:C8" totalsRowShown="0">
+  <autoFilter ref="A1:C8" xr:uid="{BA93B42F-9927-452E-9F15-AB8EAAC0F454}"/>
+  <tableColumns count="3">
+    <tableColumn id="1" xr3:uid="{34449552-06D0-4181-96E6-3E0C84E41B70}" name="k"/>
+    <tableColumn id="2" xr3:uid="{3B3C1BFA-F2F4-4406-9001-E694A34D2E78}" name="n"/>
+    <tableColumn id="3" xr3:uid="{2397E818-8931-4F3F-A8CA-8EDBDAC7A47D}" name="m"/>
+  </tableColumns>
+  <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+</table>
+</file>
+
+<file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{A2BFC831-74A5-47D2-AF2A-243C35BE968C}" name="TTableTotals" displayName="TTableTotals" ref="A1:C6" totalsRowCount="1">
+  <autoFilter ref="A1:C5" xr:uid="{A2BFC831-74A5-47D2-AF2A-243C35BE968C}"/>
+  <tableColumns count="3">
+    <tableColumn id="1" xr3:uid="{0F458D48-74AF-4BB9-A567-BA917F5895CF}" name="k" totalsRowLabel="Total"/>
+    <tableColumn id="2" xr3:uid="{62926DF0-C0CA-407A-81E3-9CF28FFC8685}" name="n" totalsRowFunction="sum" totalsRowDxfId="0"/>
+    <tableColumn id="3" xr3:uid="{2661A755-93BB-405E-BEC5-96710D917A76}" name="m" totalsRowFunction="count"/>
+  </tableColumns>
+  <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+</table>
+</file>
+
+<file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{AB70B1AD-596B-4433-A633-0E63DE5A6BD1}" name="TTableTotalsShapes" displayName="TTableTotalsShapes" ref="A1:C6" totalsRowCount="1">
+  <autoFilter ref="A1:C5" xr:uid="{AB70B1AD-596B-4433-A633-0E63DE5A6BD1}"/>
+  <tableColumns count="3">
+    <tableColumn id="1" xr3:uid="{DD778B9E-3E56-4BDB-A114-A82D6C456788}" name="k" totalsRowLabel="Total"/>
+    <tableColumn id="2" xr3:uid="{6A9843CF-4943-4328-A542-7082BF8D3D6C}" name="n" totalsRowFunction="sum"/>
+    <tableColumn id="3" xr3:uid="{F4D8699F-3AA0-4756-9E04-80F2206C364A}" name="m" totalsRowFunction="count"/>
+  </tableColumns>
+  <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+</table>
+</file>
+
+<file path=xl/tables/table4.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="4" xr:uid="{6B7D6AEA-E1FE-40D2-817B-534A0F4F5D18}" name="TTableInner" displayName="TTableInner" ref="A1:C5" totalsRowShown="0">
+  <autoFilter ref="A1:C5" xr:uid="{6B7D6AEA-E1FE-40D2-817B-534A0F4F5D18}"/>
+  <tableColumns count="3">
+    <tableColumn id="1" xr3:uid="{28DD4C60-5BCC-4D09-A213-7F175B4B0833}" name="k"/>
+    <tableColumn id="2" xr3:uid="{50BD1794-2F11-4E91-87CA-A7D492F97BEE}" name="n"/>
+    <tableColumn id="3" xr3:uid="{3D3CE7BA-6356-47CC-BE40-48A1F5990CA7}" name="m"/>
+  </tableColumns>
+  <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+</table>
+</file>
+
+<file path=xl/tables/table5.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="5" xr:uid="{7CBC7FC0-E877-4FF6-B25B-DBEC71FC438F}" name="TTableCell" displayName="TTableCell" ref="A1:C5" totalsRowShown="0">
+  <autoFilter ref="A1:C5" xr:uid="{7CBC7FC0-E877-4FF6-B25B-DBEC71FC438F}"/>
+  <tableColumns count="3">
+    <tableColumn id="1" xr3:uid="{EE0EE49D-6478-42A7-998C-6793152DDE02}" name="k"/>
+    <tableColumn id="2" xr3:uid="{FE1895D6-CBB5-4B5A-9C69-99AEF6FF47B2}" name="n"/>
+    <tableColumn id="3" xr3:uid="{5216E245-6917-46B4-82D0-0969035D6791}" name="m"/>
+  </tableColumns>
+  <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+</table>
+</file>
+
+<file path=xl/tables/table6.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="6" xr:uid="{36D25F1D-7283-49A3-9DB2-B6481474753B}" name="TTableNoHeaderAsked" displayName="TTableNoHeaderAsked" ref="A1:C5" totalsRowShown="0">
+  <autoFilter ref="A1:C5" xr:uid="{36D25F1D-7283-49A3-9DB2-B6481474753B}"/>
+  <tableColumns count="3">
+    <tableColumn id="1" xr3:uid="{974E34DD-1A3F-4767-BDAC-09183E46A093}" name="k"/>
+    <tableColumn id="2" xr3:uid="{C486837E-8A30-4450-8D14-0E4A518AC5EE}" name="n"/>
+    <tableColumn id="3" xr3:uid="{5476EC6B-3CF4-4683-AFEB-866DEFBD1260}" name="m"/>
+  </tableColumns>
+  <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+</table>
+</file>
+
+<file path=xl/tables/table7.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="7" xr:uid="{93F7C00B-FD4B-4D8F-B9CC-08BD1C17FFDD}" name="TTableTotalsRow" displayName="TTableTotalsRow" ref="A1:C6" totalsRowCount="1">
+  <autoFilter ref="A1:C5" xr:uid="{93F7C00B-FD4B-4D8F-B9CC-08BD1C17FFDD}"/>
+  <tableColumns count="3">
+    <tableColumn id="1" xr3:uid="{87A34A19-799A-475C-B024-6D3ECD9B713B}" name="k" totalsRowLabel="Total"/>
+    <tableColumn id="2" xr3:uid="{FDBDFE70-7CE0-4E85-97D6-AE423123A225}" name="n" totalsRowFunction="sum"/>
+    <tableColumn id="3" xr3:uid="{F5431527-B110-4F8D-BB0A-5BB5C00F614A}" name="m" totalsRowFunction="count"/>
+  </tableColumns>
+  <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+</table>
+</file>
+
+<file path=xl/tables/table8.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="8" xr:uid="{774C4179-6A08-4994-8F55-DA2ACFD09E9F}" name="TTableCalc" displayName="TTableCalc" ref="A1:D5" totalsRowShown="0">
+  <autoFilter ref="A1:D5" xr:uid="{774C4179-6A08-4994-8F55-DA2ACFD09E9F}"/>
+  <tableColumns count="4">
+    <tableColumn id="1" xr3:uid="{174F224F-3BE3-4622-A143-F35A4F61E664}" name="k"/>
+    <tableColumn id="2" xr3:uid="{C37E01AB-BEE0-4389-B03F-B2A9745BB785}" name="n"/>
+    <tableColumn id="3" xr3:uid="{28CE6C6B-1819-4F9F-B6A5-8E5F480141C6}" name="m"/>
+    <tableColumn id="4" xr3:uid="{23A31060-32C4-4B26-B23B-4972DC6D3F92}" name="calc">
+      <calculatedColumnFormula>TTableCalc[[#This Row],[k]]&amp;TTableCalc[[#This Row],[n]]</calculatedColumnFormula>
+    </tableColumn>
+  </tableColumns>
+  <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+</table>
+</file>
+
+<file path=xl/tables/table9.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="9" xr:uid="{9680B6E2-FCAC-45CD-BF36-CB4D7413921C}" name="TTableHidden" displayName="TTableHidden" ref="A1:C5" totalsRowShown="0">
+  <autoFilter ref="A1:C5" xr:uid="{9680B6E2-FCAC-45CD-BF36-CB4D7413921C}"/>
+  <tableColumns count="3">
+    <tableColumn id="1" xr3:uid="{0048F738-649E-44CD-8B79-C86A48345FA9}" name="k"/>
+    <tableColumn id="2" xr3:uid="{E4E7A54E-CA88-4119-AA57-9015DC3E66EE}" name="n"/>
+    <tableColumn id="3" xr3:uid="{8E38363A-2323-4D26-B700-EDCD00675371}" name="m"/>
+  </tableColumns>
+  <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+</table>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -785,12 +1491,12 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3BE099DC-0478-48C5-BCC0-2FBC9D2AAAA1}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8D8D77A5-D8DE-40C3-A0D4-4B46DE50B2EC}">
   <sheetPr codeName="Sheet1"/>
   <dimension ref="A1:B367"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -798,7 +1504,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2">
         <v>1</v>
       </c>
@@ -806,7 +1512,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>0</v>
       </c>
@@ -814,7 +1520,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A6">
         <v>1</v>
       </c>
@@ -822,7 +1528,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A7">
         <f>1+2^-52</f>
         <v>1.0000000000000002</v>
@@ -831,7 +1537,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>0</v>
       </c>
@@ -839,7 +1545,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A10">
         <v>0.1</v>
       </c>
@@ -847,7 +1553,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A11">
         <f>0.3-0.2</f>
         <v>9.9999999999999978E-2</v>
@@ -856,7 +1562,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="13" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>0</v>
       </c>
@@ -864,7 +1570,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="14" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A14">
         <v>1</v>
       </c>
@@ -872,7 +1578,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="15" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A15" s="1">
         <v>1</v>
       </c>
@@ -880,7 +1586,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="17" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
         <v>0</v>
       </c>
@@ -888,7 +1594,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="18" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A18" s="2">
         <v>43845</v>
       </c>
@@ -896,7 +1602,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="19" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A19">
         <v>43845</v>
       </c>
@@ -904,7 +1610,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="21" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="21" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
         <v>0</v>
       </c>
@@ -912,7 +1618,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="22" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="22" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A22" s="2">
         <v>43845</v>
       </c>
@@ -920,7 +1626,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="23" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="23" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A23" s="3">
         <v>43845</v>
       </c>
@@ -928,7 +1634,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="25" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="25" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
         <v>0</v>
       </c>
@@ -936,7 +1642,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="26" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="26" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A26">
         <v>1.23456789012345</v>
       </c>
@@ -944,7 +1650,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="27" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="27" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A27">
         <v>1.23456789012346</v>
       </c>
@@ -952,7 +1658,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="29" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="29" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
         <v>0</v>
       </c>
@@ -960,7 +1666,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="30" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="30" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A30">
         <v>12345678901</v>
       </c>
@@ -968,7 +1674,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="31" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="31" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A31">
         <v>12345678902</v>
       </c>
@@ -976,7 +1682,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="33" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="33" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
         <v>0</v>
       </c>
@@ -984,7 +1690,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="34" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="34" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A34">
         <v>123456789012</v>
       </c>
@@ -992,7 +1698,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="35" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="35" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A35">
         <v>123456789013</v>
       </c>
@@ -1000,7 +1706,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="37" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="37" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
         <v>0</v>
       </c>
@@ -1008,7 +1714,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="38" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="38" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A38" s="4">
         <v>1.5</v>
       </c>
@@ -1016,7 +1722,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="39" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="39" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A39">
         <v>2</v>
       </c>
@@ -1024,7 +1730,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="41" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="41" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
         <v>0</v>
       </c>
@@ -1032,7 +1738,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="42" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="42" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A42" s="4">
         <v>2</v>
       </c>
@@ -1040,7 +1746,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="45" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="45" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
         <v>0</v>
       </c>
@@ -1048,7 +1754,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="46" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="46" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A46" s="4">
         <v>1.5</v>
       </c>
@@ -1056,7 +1762,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="47" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="47" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A47" s="5">
         <v>1.5</v>
       </c>
@@ -1064,7 +1770,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="49" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="49" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
         <v>0</v>
       </c>
@@ -1072,7 +1778,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="50" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="50" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A50" s="6">
         <v>1E+20</v>
       </c>
@@ -1080,7 +1786,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="51" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="51" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A51">
         <v>1E+20</v>
       </c>
@@ -1088,7 +1794,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="53" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="53" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A53" t="s">
         <v>0</v>
       </c>
@@ -1096,7 +1802,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="54" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="54" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A54" s="7">
         <v>0.5</v>
       </c>
@@ -1104,7 +1810,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="55" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="55" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A55">
         <v>0.5</v>
       </c>
@@ -1112,7 +1818,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="57" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="57" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A57" t="s">
         <v>0</v>
       </c>
@@ -1120,7 +1826,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="58" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="58" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A58" s="7">
         <v>0.5</v>
       </c>
@@ -1128,7 +1834,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="61" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="61" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A61" t="s">
         <v>0</v>
       </c>
@@ -1136,7 +1842,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="62" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="62" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A62" s="7">
         <v>0.5</v>
       </c>
@@ -1144,7 +1850,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="63" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="63" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A63" s="8">
         <v>0.5</v>
       </c>
@@ -1152,7 +1858,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="65" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="65" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A65" t="s">
         <v>0</v>
       </c>
@@ -1160,7 +1866,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="66" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="66" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A66" s="2">
         <v>43845</v>
       </c>
@@ -1168,7 +1874,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="67" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="67" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A67" s="2">
         <v>43845.5</v>
       </c>
@@ -1176,7 +1882,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="69" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="69" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A69" t="s">
         <v>0</v>
       </c>
@@ -1184,7 +1890,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="70" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="70" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A70" s="9">
         <v>0.5</v>
       </c>
@@ -1192,7 +1898,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="71" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="71" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A71" s="9">
         <v>0.50000009999999995</v>
       </c>
@@ -1200,7 +1906,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="73" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="73" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A73" t="s">
         <v>0</v>
       </c>
@@ -1208,7 +1914,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="74" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="74" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A74">
         <v>1</v>
       </c>
@@ -1216,7 +1922,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="77" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="77" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A77" t="s">
         <v>0</v>
       </c>
@@ -1224,7 +1930,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="78" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="78" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A78" s="4">
         <v>1</v>
       </c>
@@ -1232,7 +1938,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="81" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="81" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A81" t="s">
         <v>0</v>
       </c>
@@ -1240,7 +1946,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="82" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="82" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A82" s="11">
         <v>-1</v>
       </c>
@@ -1248,7 +1954,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="83" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="83" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A83">
         <v>1</v>
       </c>
@@ -1256,7 +1962,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="85" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="85" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A85" t="s">
         <v>0</v>
       </c>
@@ -1264,7 +1970,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="86" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="86" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A86" s="11">
         <v>-1</v>
       </c>
@@ -1272,7 +1978,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="87" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="87" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A87">
         <v>-1</v>
       </c>
@@ -1280,7 +1986,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="89" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="89" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A89" t="s">
         <v>0</v>
       </c>
@@ -1288,7 +1994,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="90" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="90" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A90" s="12">
         <v>1234</v>
       </c>
@@ -1296,7 +2002,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="91" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="91" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A91" s="4">
         <v>1234</v>
       </c>
@@ -1304,7 +2010,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="93" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="93" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A93" t="s">
         <v>0</v>
       </c>
@@ -1312,7 +2018,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="94" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="94" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A94" s="13">
         <v>1234</v>
       </c>
@@ -1320,7 +2026,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="97" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="97" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A97" t="s">
         <v>0</v>
       </c>
@@ -1328,7 +2034,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="98" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="98" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A98">
         <f>1</f>
         <v>1</v>
@@ -1337,7 +2043,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="101" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="101" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A101" t="s">
         <v>0</v>
       </c>
@@ -1345,7 +2051,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="102" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="102" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A102">
         <v>0</v>
       </c>
@@ -1353,7 +2059,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="105" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="105" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A105" t="s">
         <v>0</v>
       </c>
@@ -1361,7 +2067,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="106" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="106" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A106">
         <v>1</v>
       </c>
@@ -1369,7 +2075,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="107" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="107" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A107" t="str">
         <f>"1"</f>
         <v>1</v>
@@ -1378,7 +2084,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="109" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="109" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A109" t="s">
         <v>0</v>
       </c>
@@ -1386,7 +2092,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="110" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="110" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A110">
         <v>1</v>
       </c>
@@ -1394,7 +2100,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="111" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="111" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A111" s="14" t="s">
         <v>4</v>
       </c>
@@ -1402,7 +2108,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="113" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="113" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A113" t="s">
         <v>0</v>
       </c>
@@ -1410,7 +2116,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="114" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="114" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A114">
         <v>1</v>
       </c>
@@ -1418,7 +2124,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="115" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="115" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A115" s="10" t="s">
         <v>4</v>
       </c>
@@ -1426,7 +2132,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="117" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="117" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A117" t="s">
         <v>0</v>
       </c>
@@ -1434,7 +2140,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="118" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="118" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A118">
         <v>1</v>
       </c>
@@ -1442,7 +2148,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="119" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="119" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A119" t="b">
         <v>1</v>
       </c>
@@ -1450,7 +2156,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="121" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="121" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A121" t="s">
         <v>0</v>
       </c>
@@ -1458,7 +2164,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="122" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="122" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A122">
         <v>0</v>
       </c>
@@ -1466,7 +2172,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="123" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="123" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A123" t="b">
         <v>0</v>
       </c>
@@ -1474,7 +2180,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="125" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="125" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A125" t="s">
         <v>0</v>
       </c>
@@ -1482,7 +2188,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="126" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="126" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A126" s="14" t="s">
         <v>5</v>
       </c>
@@ -1490,7 +2196,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="127" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="127" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A127" s="2">
         <v>43845</v>
       </c>
@@ -1498,7 +2204,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="129" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="129" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A129" t="s">
         <v>0</v>
       </c>
@@ -1506,7 +2212,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="130" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="130" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A130" s="14" t="s">
         <v>6</v>
       </c>
@@ -1514,7 +2220,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="131" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="131" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A131" s="1">
         <v>43845</v>
       </c>
@@ -1522,7 +2228,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="133" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="133" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A133" t="s">
         <v>0</v>
       </c>
@@ -1530,7 +2236,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="134" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="134" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A134" t="s">
         <v>7</v>
       </c>
@@ -1538,7 +2244,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="137" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="137" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A137" t="s">
         <v>0</v>
       </c>
@@ -1546,7 +2252,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="138" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="138" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A138" t="s">
         <v>7</v>
       </c>
@@ -1554,7 +2260,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="141" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="141" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A141" t="s">
         <v>0</v>
       </c>
@@ -1562,7 +2268,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="142" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="142" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A142" s="14" t="s">
         <v>8</v>
       </c>
@@ -1570,7 +2276,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="145" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="145" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A145" t="s">
         <v>0</v>
       </c>
@@ -1578,7 +2284,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="146" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="146" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A146" s="14" t="s">
         <v>9</v>
       </c>
@@ -1586,7 +2292,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="149" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="149" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A149" t="s">
         <v>0</v>
       </c>
@@ -1594,7 +2300,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="150" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="150" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A150" s="14" t="s">
         <v>9</v>
       </c>
@@ -1602,7 +2308,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="153" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="153" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A153" t="s">
         <v>0</v>
       </c>
@@ -1610,7 +2316,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="154" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="154" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A154" s="14" t="s">
         <v>10</v>
       </c>
@@ -1618,7 +2324,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="155" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="155" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A155" s="14" t="s">
         <v>11</v>
       </c>
@@ -1626,7 +2332,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="157" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="157" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A157" t="s">
         <v>0</v>
       </c>
@@ -1634,7 +2340,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="158" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="158" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A158" s="14" t="s">
         <v>12</v>
       </c>
@@ -1642,7 +2348,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="159" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="159" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A159" s="14" t="s">
         <v>13</v>
       </c>
@@ -1650,7 +2356,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="161" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="161" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A161" t="s">
         <v>0</v>
       </c>
@@ -1658,7 +2364,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="162" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="162" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A162" s="14" t="s">
         <v>14</v>
       </c>
@@ -1666,7 +2372,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="163" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="163" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A163" s="14" t="s">
         <v>15</v>
       </c>
@@ -1674,7 +2380,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="165" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="165" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A165" t="s">
         <v>0</v>
       </c>
@@ -1682,7 +2388,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="166" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="166" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A166" s="14" t="s">
         <v>16</v>
       </c>
@@ -1690,7 +2396,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="167" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="167" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A167" s="14" t="s">
         <v>7</v>
       </c>
@@ -1698,7 +2404,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="169" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="169" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A169" t="s">
         <v>0</v>
       </c>
@@ -1706,7 +2412,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="170" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="170" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A170" s="14" t="s">
         <v>17</v>
       </c>
@@ -1714,7 +2420,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="171" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="171" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A171" s="14" t="s">
         <v>18</v>
       </c>
@@ -1722,7 +2428,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="173" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="173" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A173" t="s">
         <v>0</v>
       </c>
@@ -1730,7 +2436,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="174" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="174" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A174" s="14" t="s">
         <v>19</v>
       </c>
@@ -1738,7 +2444,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="175" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="175" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A175" s="14" t="s">
         <v>4</v>
       </c>
@@ -1746,7 +2452,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="177" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="177" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A177" t="s">
         <v>0</v>
       </c>
@@ -1754,7 +2460,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="178" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="178" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A178" s="14" t="s">
         <v>20</v>
       </c>
@@ -1762,7 +2468,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="181" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="181" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A181" t="s">
         <v>0</v>
       </c>
@@ -1770,7 +2476,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="182" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="182" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A182" s="14" t="s">
         <v>21</v>
       </c>
@@ -1778,7 +2484,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="185" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="185" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A185" t="s">
         <v>0</v>
       </c>
@@ -1786,7 +2492,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="186" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="186" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A186" s="14" t="s">
         <v>22</v>
       </c>
@@ -1794,7 +2500,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="189" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="189" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A189" t="s">
         <v>0</v>
       </c>
@@ -1802,7 +2508,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="190" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="190" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A190" s="14" t="s">
         <v>23</v>
       </c>
@@ -1810,7 +2516,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="193" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="193" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A193" t="s">
         <v>0</v>
       </c>
@@ -1818,7 +2524,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="194" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="194" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A194" s="14" t="s">
         <v>24</v>
       </c>
@@ -1826,7 +2532,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="197" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="197" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A197" t="s">
         <v>0</v>
       </c>
@@ -1834,7 +2540,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="198" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="198" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A198" s="14" t="s">
         <v>25</v>
       </c>
@@ -1842,7 +2548,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="201" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="201" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A201" t="s">
         <v>0</v>
       </c>
@@ -1850,7 +2556,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="202" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="202" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A202" s="14" t="s">
         <v>26</v>
       </c>
@@ -1858,7 +2564,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="203" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="203" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A203" s="14" t="s">
         <v>13</v>
       </c>
@@ -1866,7 +2572,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="205" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="205" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A205" t="s">
         <v>0</v>
       </c>
@@ -1874,7 +2580,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="206" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="206" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A206" s="14" t="s">
         <v>27</v>
       </c>
@@ -1882,7 +2588,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="207" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="207" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A207" s="14" t="s">
         <v>13</v>
       </c>
@@ -1890,7 +2596,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="209" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="209" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A209" t="s">
         <v>0</v>
       </c>
@@ -1898,7 +2604,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="210" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="210" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A210" s="14" t="s">
         <v>28</v>
       </c>
@@ -1906,7 +2612,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="211" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="211" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A211" s="14" t="s">
         <v>12</v>
       </c>
@@ -1914,7 +2620,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="213" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="213" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A213" t="s">
         <v>0</v>
       </c>
@@ -1922,7 +2628,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="214" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="214" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A214" s="14" t="s">
         <v>29</v>
       </c>
@@ -1930,7 +2636,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="217" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="217" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A217" t="s">
         <v>0</v>
       </c>
@@ -1938,7 +2644,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="218" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="218" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A218" s="14" t="s">
         <v>30</v>
       </c>
@@ -1946,7 +2652,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="221" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="221" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A221" t="s">
         <v>0</v>
       </c>
@@ -1954,7 +2660,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="222" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="222" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A222" s="14" t="s">
         <v>31</v>
       </c>
@@ -1962,7 +2668,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="225" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="225" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A225" t="s">
         <v>0</v>
       </c>
@@ -1970,7 +2676,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="226" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="226" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A226" s="14" t="s">
         <v>32</v>
       </c>
@@ -1978,7 +2684,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="227" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="227" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A227" s="14" t="s">
         <v>33</v>
       </c>
@@ -1986,7 +2692,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="229" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="229" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A229" t="s">
         <v>0</v>
       </c>
@@ -1994,7 +2700,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="230" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="230" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A230" s="14" t="s">
         <v>34</v>
       </c>
@@ -2002,7 +2708,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="231" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="231" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A231" s="14" t="s">
         <v>35</v>
       </c>
@@ -2010,7 +2716,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="233" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="233" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A233" t="s">
         <v>0</v>
       </c>
@@ -2018,7 +2724,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="234" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="234" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A234" s="14" t="s">
         <v>36</v>
       </c>
@@ -2026,7 +2732,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="235" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="235" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A235" s="14" t="s">
         <v>37</v>
       </c>
@@ -2034,7 +2740,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="237" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="237" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A237" t="s">
         <v>0</v>
       </c>
@@ -2042,7 +2748,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="238" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="238" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A238" s="14" t="s">
         <v>38</v>
       </c>
@@ -2050,7 +2756,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="239" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="239" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A239" s="14" t="s">
         <v>4</v>
       </c>
@@ -2058,7 +2764,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="241" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="241" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A241" t="s">
         <v>0</v>
       </c>
@@ -2066,7 +2772,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="242" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="242" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A242" s="14" t="s">
         <v>39</v>
       </c>
@@ -2074,7 +2780,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="243" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="243" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A243" s="14" t="s">
         <v>40</v>
       </c>
@@ -2082,7 +2788,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="245" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="245" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A245" t="s">
         <v>0</v>
       </c>
@@ -2090,7 +2796,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="246" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="246" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A246" s="14" t="s">
         <v>41</v>
       </c>
@@ -2098,7 +2804,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="247" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="247" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A247" s="14" t="s">
         <v>35</v>
       </c>
@@ -2106,7 +2812,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="249" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="249" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A249" t="s">
         <v>0</v>
       </c>
@@ -2114,7 +2820,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="250" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="250" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A250" s="14" t="s">
         <v>42</v>
       </c>
@@ -2122,7 +2828,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="251" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="251" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A251" s="14" t="s">
         <v>43</v>
       </c>
@@ -2130,7 +2836,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="253" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="253" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A253" t="s">
         <v>0</v>
       </c>
@@ -2138,7 +2844,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="254" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="254" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A254" s="14" t="s">
         <v>44</v>
       </c>
@@ -2146,7 +2852,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="257" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="257" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A257" t="s">
         <v>0</v>
       </c>
@@ -2154,7 +2860,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="258" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="258" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A258" s="14" t="s">
         <v>45</v>
       </c>
@@ -2162,7 +2868,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="261" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="261" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A261" t="s">
         <v>0</v>
       </c>
@@ -2170,7 +2876,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="262" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="262" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A262" s="14" t="s">
         <v>46</v>
       </c>
@@ -2178,7 +2884,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="263" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="263" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A263" s="14" t="s">
         <v>47</v>
       </c>
@@ -2186,7 +2892,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="265" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="265" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A265" t="s">
         <v>0</v>
       </c>
@@ -2194,7 +2900,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="266" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="266" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A266" s="14" t="s">
         <v>48</v>
       </c>
@@ -2202,7 +2908,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="267" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="267" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A267" s="14" t="s">
         <v>46</v>
       </c>
@@ -2210,7 +2916,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="269" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="269" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A269" t="s">
         <v>0</v>
       </c>
@@ -2218,7 +2924,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="270" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="270" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A270" s="14" t="s">
         <v>49</v>
       </c>
@@ -2226,7 +2932,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="273" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="273" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A273" t="s">
         <v>0</v>
       </c>
@@ -2234,7 +2940,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="274" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="274" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A274" s="14" t="s">
         <v>50</v>
       </c>
@@ -2242,7 +2948,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="277" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="277" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A277" t="s">
         <v>0</v>
       </c>
@@ -2250,7 +2956,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="278" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="278" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A278" s="14" t="s">
         <v>51</v>
       </c>
@@ -2258,7 +2964,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="279" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="279" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A279" s="14" t="s">
         <v>52</v>
       </c>
@@ -2266,7 +2972,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="281" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="281" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A281" t="s">
         <v>0</v>
       </c>
@@ -2274,7 +2980,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="282" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="282" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A282" s="14" t="s">
         <v>53</v>
       </c>
@@ -2282,7 +2988,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="283" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="283" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A283" s="14" t="s">
         <v>54</v>
       </c>
@@ -2290,7 +2996,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="285" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="285" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A285" t="s">
         <v>0</v>
       </c>
@@ -2298,7 +3004,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="286" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="286" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A286" s="14" t="s">
         <v>55</v>
       </c>
@@ -2306,7 +3012,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="287" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="287" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A287" s="14" t="s">
         <v>56</v>
       </c>
@@ -2314,7 +3020,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="289" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="289" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A289" t="s">
         <v>0</v>
       </c>
@@ -2322,7 +3028,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="290" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="290" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A290" s="14" t="s">
         <v>57</v>
       </c>
@@ -2330,7 +3036,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="291" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="291" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A291" s="14" t="s">
         <v>58</v>
       </c>
@@ -2338,7 +3044,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="293" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="293" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A293" t="s">
         <v>0</v>
       </c>
@@ -2346,7 +3052,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="294" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="294" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A294" s="14" t="s">
         <v>59</v>
       </c>
@@ -2354,7 +3060,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="295" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="295" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A295" s="14" t="s">
         <v>60</v>
       </c>
@@ -2362,7 +3068,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="297" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="297" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A297" t="s">
         <v>0</v>
       </c>
@@ -2370,7 +3076,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="298" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="298" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A298" s="15" t="s">
         <v>7</v>
       </c>
@@ -2378,7 +3084,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="301" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="301" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A301" t="s">
         <v>0</v>
       </c>
@@ -2386,7 +3092,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="302" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="302" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A302" s="15" t="s">
         <v>7</v>
       </c>
@@ -2394,7 +3100,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="305" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="305" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A305" t="s">
         <v>0</v>
       </c>
@@ -2402,7 +3108,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="306" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="306" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A306" s="16" t="s">
         <v>7</v>
       </c>
@@ -2410,7 +3116,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="307" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="307" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A307" s="14" t="s">
         <v>16</v>
       </c>
@@ -2418,7 +3124,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="309" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="309" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A309" t="s">
         <v>0</v>
       </c>
@@ -2426,7 +3132,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="310" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="310" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A310" t="b">
         <v>1</v>
       </c>
@@ -2434,7 +3140,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="313" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="313" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A313" t="s">
         <v>0</v>
       </c>
@@ -2442,7 +3148,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="314" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="314" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A314" t="b">
         <v>1</v>
       </c>
@@ -2450,7 +3156,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="317" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="317" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A317" t="s">
         <v>0</v>
       </c>
@@ -2458,7 +3164,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="318" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="318" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A318" t="b">
         <v>0</v>
       </c>
@@ -2466,7 +3172,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="321" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="321" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A321" t="s">
         <v>0</v>
       </c>
@@ -2474,7 +3180,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="322" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="322" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A322" t="b">
         <v>1</v>
       </c>
@@ -2482,7 +3188,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="325" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="325" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A325" t="s">
         <v>0</v>
       </c>
@@ -2490,7 +3196,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="326" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="326" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A326" s="1" t="b">
         <v>1</v>
       </c>
@@ -2498,7 +3204,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="329" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="329" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A329" t="s">
         <v>0</v>
       </c>
@@ -2506,7 +3212,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="330" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="330" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A330" t="e">
         <v>#N/A</v>
       </c>
@@ -2514,7 +3220,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="331" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="331" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A331" s="14" t="s">
         <v>61</v>
       </c>
@@ -2522,7 +3228,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="333" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="333" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A333" t="s">
         <v>0</v>
       </c>
@@ -2530,7 +3236,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="334" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="334" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A334" t="e">
         <v>#N/A</v>
       </c>
@@ -2538,7 +3244,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="337" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="337" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A337" t="s">
         <v>0</v>
       </c>
@@ -2546,7 +3252,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="338" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="338" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A338" t="e">
         <v>#N/A</v>
       </c>
@@ -2554,7 +3260,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="339" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="339" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A339" t="e">
         <v>#DIV/0!</v>
       </c>
@@ -2562,7 +3268,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="341" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="341" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A341" t="s">
         <v>0</v>
       </c>
@@ -2570,7 +3276,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="342" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="342" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A342" t="e">
         <f>1/0</f>
         <v>#DIV/0!</v>
@@ -2579,7 +3285,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="345" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="345" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A345" t="s">
         <v>0</v>
       </c>
@@ -2587,12 +3293,12 @@
         <v>1</v>
       </c>
     </row>
-    <row r="346" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="346" spans="1:2" x14ac:dyDescent="0.25">
       <c r="B346" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="349" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="349" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A349" t="s">
         <v>0</v>
       </c>
@@ -2600,12 +3306,12 @@
         <v>1</v>
       </c>
     </row>
-    <row r="350" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="350" spans="1:2" x14ac:dyDescent="0.25">
       <c r="B350" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="351" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="351" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A351" t="str">
         <f>""</f>
         <v/>
@@ -2614,7 +3320,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="353" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="353" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A353" t="s">
         <v>0</v>
       </c>
@@ -2622,7 +3328,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="354" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="354" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A354" t="str">
         <f>""</f>
         <v/>
@@ -2631,7 +3337,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="357" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="357" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A357" t="s">
         <v>0</v>
       </c>
@@ -2639,12 +3345,12 @@
         <v>1</v>
       </c>
     </row>
-    <row r="358" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="358" spans="1:2" x14ac:dyDescent="0.25">
       <c r="B358" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="359" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="359" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A359" s="14" t="s">
         <v>62</v>
       </c>
@@ -2652,7 +3358,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="361" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="361" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A361" t="s">
         <v>0</v>
       </c>
@@ -2660,12 +3366,12 @@
         <v>1</v>
       </c>
     </row>
-    <row r="362" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="362" spans="1:2" x14ac:dyDescent="0.25">
       <c r="B362" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="363" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="363" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A363">
         <v>0</v>
       </c>
@@ -2673,7 +3379,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="365" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="365" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A365" t="s">
         <v>0</v>
       </c>
@@ -2681,12 +3387,12 @@
         <v>1</v>
       </c>
     </row>
-    <row r="366" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="366" spans="1:2" x14ac:dyDescent="0.25">
       <c r="B366" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="367" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="367" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A367" s="14" t="s">
         <v>63</v>
       </c>
@@ -2700,11 +3406,11 @@
 </file>
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9B50330C-5C32-4A8D-8292-575E0EA70AFF}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C5C27977-A79E-4620-BCDB-060B036925B1}">
   <dimension ref="A1:B4"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>64</v>
       </c>
@@ -2712,7 +3418,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>7</v>
       </c>
@@ -2720,7 +3426,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>80</v>
       </c>
@@ -2728,7 +3434,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>68</v>
       </c>
@@ -2742,11 +3448,11 @@
 </file>
 
 <file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E61348C1-3FAD-4993-A47C-9C0DBA313D6D}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A50C747A-FC69-4C6F-9261-24AA458C57F8}">
   <dimension ref="A1:C4"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>64</v>
       </c>
@@ -2754,7 +3460,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>7</v>
       </c>
@@ -2762,7 +3468,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>80</v>
       </c>
@@ -2774,7 +3480,7 @@
         <v>#VALUE!</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>68</v>
       </c>
@@ -2788,11 +3494,11 @@
 </file>
 
 <file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E620705C-A89A-4CB7-AEF7-853C747EFA6F}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CE1ABBAB-2937-4BA7-A2F3-1927558BFAAC}">
   <dimension ref="A1:C5"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>64</v>
       </c>
@@ -2800,7 +3506,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>7</v>
       </c>
@@ -2808,7 +3514,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>80</v>
       </c>
@@ -2816,7 +3522,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>68</v>
       </c>
@@ -2834,11 +3540,11 @@
 </file>
 
 <file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{231405A5-8CD4-4528-8649-0FC50557B5FE}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A9A83698-971C-4F0E-ADEA-AC5171E76E39}">
   <dimension ref="A1:C5"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>64</v>
       </c>
@@ -2846,7 +3552,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>7</v>
       </c>
@@ -2854,7 +3560,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>80</v>
       </c>
@@ -2862,7 +3568,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>68</v>
       </c>
@@ -2880,11 +3586,11 @@
 </file>
 
 <file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7E76157E-7CEE-431D-AF37-1D16A1C5DF8B}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CE8BE7E6-D131-439A-840A-0252C96CA25B}">
   <dimension ref="A1:C4"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>64</v>
       </c>
@@ -2892,7 +3598,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>7</v>
       </c>
@@ -2900,7 +3606,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>80</v>
       </c>
@@ -2908,7 +3614,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>68</v>
       </c>
@@ -2926,11 +3632,11 @@
 </file>
 
 <file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E2C71B9F-DECF-401D-9012-4851DBE0A279}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{97514A65-2046-4999-B803-962E1D93ADCB}">
   <dimension ref="A1:B4"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>64</v>
       </c>
@@ -2938,7 +3644,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>7</v>
       </c>
@@ -2946,7 +3652,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>80</v>
       </c>
@@ -2954,7 +3660,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>68</v>
       </c>
@@ -2964,7 +3670,7 @@
     </row>
   </sheetData>
   <dataValidations count="1">
-    <dataValidation type="whole" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="B2:B5 B12" xr:uid="{2C925C5C-25FB-433B-9C06-6D3974E21C1A}">
+    <dataValidation type="whole" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="B2:B5 B12" xr:uid="{64748F43-FDB9-491F-91A2-4676E666CB96}">
       <formula1>0</formula1>
       <formula2>9</formula2>
     </dataValidation>
@@ -2973,12 +3679,12 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{80998A49-51B0-4E72-AA4E-CF3A65115B39}">
-  <dimension ref="A1:E11"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+<file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{678F0603-161C-4FB4-A450-83435F30D592}">
+  <dimension ref="A1:H13"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>64</v>
       </c>
@@ -2986,92 +3692,708 @@
         <v>67</v>
       </c>
       <c r="C1" t="s">
-        <v>68</v>
+        <v>1</v>
       </c>
       <c r="E1" t="s">
         <v>73</v>
       </c>
-    </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="H1" s="1">
+        <f>B7</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B2">
         <v>1</v>
       </c>
       <c r="C2" t="s">
-        <v>69</v>
+        <v>83</v>
       </c>
       <c r="E2" t="s">
         <v>74</v>
       </c>
-    </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="H2">
+        <f>SUM(B2:B5)</f>
+        <v>16</v>
+      </c>
+    </row>
+    <row r="3" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>8</v>
+        <v>80</v>
       </c>
       <c r="B3">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C3" t="s">
-        <v>70</v>
+        <v>85</v>
       </c>
       <c r="E3" t="s">
         <v>75</v>
       </c>
-    </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A4" t="s">
-        <v>65</v>
+      <c r="H3">
+        <f>SUM(B3:B8)</f>
+        <v>15</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A4" s="21" t="s">
+        <v>68</v>
       </c>
       <c r="B4">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="C4" t="s">
-        <v>71</v>
+        <v>87</v>
       </c>
       <c r="E4" t="s">
         <v>76</v>
       </c>
-    </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A5" t="s">
-        <v>66</v>
-      </c>
-      <c r="B5">
-        <v>3</v>
-      </c>
-      <c r="C5" t="s">
-        <v>72</v>
+      <c r="H4">
+        <f>SUM(A2:B5)</f>
+        <v>16</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A5" s="23" t="s">
+        <v>58</v>
+      </c>
+      <c r="B5" s="25">
+        <v>7</v>
+      </c>
+      <c r="C5">
+        <f>B5*10</f>
+        <v>70</v>
       </c>
       <c r="E5" t="s">
         <v>77</v>
       </c>
-    </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="H5">
+        <f>SUM(A1:C5)</f>
+        <v>86</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8" x14ac:dyDescent="0.25">
       <c r="E6" t="s">
         <v>78</v>
       </c>
-    </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="H6">
+        <f>SUM(B1:B5)</f>
+        <v>16</v>
+      </c>
+    </row>
+    <row r="7" spans="1:8" x14ac:dyDescent="0.25">
       <c r="E7" t="s">
         <v>79</v>
       </c>
-    </row>
-    <row r="10" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A10" t="str">
-        <f>A5&amp;B5&amp;C5</f>
-        <v>z3c6</v>
-      </c>
-      <c r="E10">
-        <f>COUNTA(A2:A7)</f>
+      <c r="H7">
+        <f>SUM(B$2:B$5)</f>
+        <v>16</v>
+      </c>
+    </row>
+    <row r="8" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="E8" t="s">
+        <v>90</v>
+      </c>
+      <c r="H8">
+        <f>SUM(A2:E8)</f>
+        <v>86</v>
+      </c>
+    </row>
+    <row r="9" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="H9">
+        <f>SUM(B6:B8)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A10" s="24"/>
+      <c r="H10">
+        <f>SUM(B4:B10)</f>
+        <v>12</v>
+      </c>
+    </row>
+    <row r="11" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="H11">
+        <f>SUM(A8:E8)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A12" t="s">
+        <v>91</v>
+      </c>
+      <c r="B12">
+        <f>SUM(B2:B5)</f>
+        <v>16</v>
+      </c>
+      <c r="C12">
+        <f>SUM(TTable[n])</f>
+        <v>16</v>
+      </c>
+      <c r="D12">
+        <f>B5</f>
+        <v>7</v>
+      </c>
+      <c r="H12" s="25">
+        <f>SUM(B8:B9)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="H13">
+        <f>$B$5</f>
+        <v>7</v>
+      </c>
+    </row>
+  </sheetData>
+  <conditionalFormatting sqref="B4:B5">
+    <cfRule type="cellIs" priority="1" stopIfTrue="1" operator="greaterThan">
+      <formula>3</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B2:B5">
+    <cfRule type="cellIs" priority="2" stopIfTrue="1" operator="greaterThan">
+      <formula>4</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="C2:C5">
+    <cfRule type="expression" priority="4" stopIfTrue="1">
+      <formula>$B2&gt;3</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A2:E5 D6:E8">
+    <cfRule type="cellIs" priority="5" stopIfTrue="1" operator="greaterThan">
+      <formula>100</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="D8:E8">
+    <cfRule type="cellIs" priority="6" stopIfTrue="1" operator="greaterThan">
+      <formula>200</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <dataValidations count="3">
+    <dataValidation type="whole" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="B2:B5" xr:uid="{4B239EFB-31C7-4210-B6A0-DD8631E4F11A}">
+      <formula1>0</formula1>
+      <formula2>9</formula2>
+    </dataValidation>
+    <dataValidation type="textLength" operator="lessThanOrEqual" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="C4:C5" xr:uid="{5628B697-240C-4651-A2F6-ED54C17D79B3}">
+      <formula1>9</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="E2:E8" xr:uid="{690A7C5A-4197-42BB-9B0B-FD21DC9265ED}">
+      <formula1>$A$2:$A$5</formula1>
+    </dataValidation>
+  </dataValidations>
+  <hyperlinks>
+    <hyperlink ref="A4" r:id="rId1" display="https://example.com/moves" xr:uid="{863D03DF-20CD-4E95-BD65-83C8C4A7CFB4}"/>
+  </hyperlinks>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <drawing r:id="rId2"/>
+  <legacyDrawing r:id="rId3"/>
+  <tableParts count="1">
+    <tablePart r:id="rId4"/>
+  </tableParts>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CAF12F49-8527-4AFA-9D06-08A3D187F5EA}">
+  <dimension ref="A1:H22"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetData>
+    <row r="1" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A1" t="s">
+        <v>64</v>
+      </c>
+      <c r="B1" t="s">
+        <v>67</v>
+      </c>
+      <c r="C1" t="s">
+        <v>1</v>
+      </c>
+      <c r="E1" t="s">
+        <v>73</v>
+      </c>
+      <c r="H1">
+        <f>B7</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>7</v>
+      </c>
+      <c r="B2">
+        <v>1</v>
+      </c>
+      <c r="C2" t="s">
+        <v>83</v>
+      </c>
+      <c r="E2" t="s">
+        <v>74</v>
+      </c>
+      <c r="H2" s="1">
+        <f>B8</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>80</v>
+      </c>
+      <c r="B3">
+        <v>3</v>
+      </c>
+      <c r="C3" t="s">
+        <v>85</v>
+      </c>
+      <c r="E3" t="s">
+        <v>75</v>
+      </c>
+      <c r="H3" s="25">
+        <f>B9</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A4" s="21" t="s">
+        <v>68</v>
+      </c>
+      <c r="B4">
+        <v>5</v>
+      </c>
+      <c r="C4" t="s">
+        <v>87</v>
+      </c>
+      <c r="E4" t="s">
+        <v>76</v>
+      </c>
+      <c r="H4" s="5">
+        <f>B6</f>
+        <v>16</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A5" s="23" t="s">
+        <v>58</v>
+      </c>
+      <c r="B5" s="25">
+        <v>7</v>
+      </c>
+      <c r="C5">
+        <f>B5*10</f>
+        <v>70</v>
+      </c>
+      <c r="E5" t="s">
+        <v>77</v>
+      </c>
+      <c r="H5">
+        <f>SUM(B2:B5)</f>
+        <v>16</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
+        <v>92</v>
+      </c>
+      <c r="B6" s="5">
+        <f>SUBTOTAL(109,TTableTotals[n])</f>
+        <v>16</v>
+      </c>
+      <c r="C6">
+        <f>SUBTOTAL(103,TTableTotals[m])</f>
         <v>4</v>
       </c>
-    </row>
-    <row r="11" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A11">
-        <f>SUM(B2:B7)</f>
-        <v>7</v>
+      <c r="E6" t="s">
+        <v>78</v>
+      </c>
+      <c r="H6">
+        <f>SUM(B3:B9)</f>
+        <v>31</v>
+      </c>
+    </row>
+    <row r="7" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="E7" t="s">
+        <v>79</v>
+      </c>
+      <c r="H7">
+        <f>SUM(A1:C5)</f>
+        <v>86</v>
+      </c>
+    </row>
+    <row r="8" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="E8" t="s">
+        <v>90</v>
+      </c>
+      <c r="H8">
+        <f>SUM(B2:B6)</f>
+        <v>32</v>
+      </c>
+    </row>
+    <row r="9" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="H9">
+        <f>SUM(A1:C6)</f>
+        <v>106</v>
+      </c>
+    </row>
+    <row r="10" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A10" s="24"/>
+      <c r="H10" s="25">
+        <f>SUM(B6:B6)</f>
+        <v>16</v>
+      </c>
+    </row>
+    <row r="11" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="H11" s="1">
+        <f>SUM(B6:B6)</f>
+        <v>16</v>
+      </c>
+    </row>
+    <row r="12" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A12" t="s">
+        <v>91</v>
+      </c>
+      <c r="B12">
+        <f>SUM(B2:B5)</f>
+        <v>16</v>
+      </c>
+      <c r="C12">
+        <f>SUM(TTableTotals[n])</f>
+        <v>16</v>
+      </c>
+      <c r="D12">
+        <f>B5</f>
+        <v>7</v>
+      </c>
+      <c r="H12">
+        <f>SUM(B6:B6)</f>
+        <v>16</v>
+      </c>
+    </row>
+    <row r="13" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="H13" s="5">
+        <f>SUM(B6:B12)</f>
+        <v>32</v>
+      </c>
+    </row>
+    <row r="14" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="H14" s="25">
+        <f>SUM(B9:B10)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="H15">
+        <f>SUM(B4:B10)</f>
+        <v>28</v>
+      </c>
+    </row>
+    <row r="16" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="H16">
+        <f>SUM(D8:E8)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17" spans="8:8" x14ac:dyDescent="0.25">
+      <c r="H17">
+        <f>SUM(D6:D8)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18" spans="8:8" x14ac:dyDescent="0.25">
+      <c r="H18">
+        <f>SUM(A9:E9)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="19" spans="8:8" x14ac:dyDescent="0.25">
+      <c r="H19">
+        <f>SUM(A6:E9)</f>
+        <v>20</v>
+      </c>
+    </row>
+    <row r="20" spans="8:8" x14ac:dyDescent="0.25">
+      <c r="H20">
+        <f>SUM(A9:C9)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21" spans="8:8" x14ac:dyDescent="0.25">
+      <c r="H21">
+        <f>SUM(A6:C6)</f>
+        <v>20</v>
+      </c>
+    </row>
+    <row r="22" spans="8:8" x14ac:dyDescent="0.25">
+      <c r="H22">
+        <f>SUM(A5:C6)</f>
+        <v>97</v>
+      </c>
+    </row>
+  </sheetData>
+  <conditionalFormatting sqref="B4:B5">
+    <cfRule type="cellIs" priority="1" stopIfTrue="1" operator="greaterThan">
+      <formula>3</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B2:B5">
+    <cfRule type="cellIs" priority="2" stopIfTrue="1" operator="greaterThan">
+      <formula>4</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="C2:C5">
+    <cfRule type="expression" priority="4" stopIfTrue="1">
+      <formula>$B2&gt;3</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A2:E5 D6:E8">
+    <cfRule type="cellIs" priority="5" stopIfTrue="1" operator="greaterThan">
+      <formula>100</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="D8:E8">
+    <cfRule type="cellIs" priority="6" stopIfTrue="1" operator="greaterThan">
+      <formula>200</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A6:C9">
+    <cfRule type="cellIs" priority="7" stopIfTrue="1" operator="greaterThan">
+      <formula>1000</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <dataValidations count="3">
+    <dataValidation type="whole" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="B2:B5" xr:uid="{8268039E-E285-40DC-B7D1-107455A73996}">
+      <formula1>0</formula1>
+      <formula2>9</formula2>
+    </dataValidation>
+    <dataValidation type="textLength" operator="lessThanOrEqual" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="C4:C5" xr:uid="{B017BE3E-0B7B-4656-BA9E-A6B611E9DA13}">
+      <formula1>9</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="E2:E8" xr:uid="{869BBE4C-5719-40B9-AFC9-6B0917D40FC2}">
+      <formula1>$A$2:$A$5</formula1>
+    </dataValidation>
+  </dataValidations>
+  <hyperlinks>
+    <hyperlink ref="A4" r:id="rId1" display="https://example.com/moves" xr:uid="{2D557415-9510-462B-B318-03E60F0AF426}"/>
+  </hyperlinks>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <drawing r:id="rId2"/>
+  <legacyDrawing r:id="rId3"/>
+  <tableParts count="1">
+    <tablePart r:id="rId4"/>
+  </tableParts>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{ECC1AE9A-384D-4189-86FB-A552CA2C0F81}">
+  <dimension ref="A1:E12"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetData>
+    <row r="1" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1" t="s">
+        <v>64</v>
+      </c>
+      <c r="B1" t="s">
+        <v>67</v>
+      </c>
+      <c r="C1" t="s">
+        <v>1</v>
+      </c>
+      <c r="E1" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>7</v>
+      </c>
+      <c r="B2">
+        <v>1</v>
+      </c>
+      <c r="C2" t="s">
+        <v>83</v>
+      </c>
+      <c r="E2" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>80</v>
+      </c>
+      <c r="B3">
+        <v>3</v>
+      </c>
+      <c r="C3" t="s">
+        <v>85</v>
+      </c>
+      <c r="E3" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
+        <v>68</v>
+      </c>
+      <c r="B4">
+        <v>5</v>
+      </c>
+      <c r="C4" t="s">
+        <v>87</v>
+      </c>
+      <c r="E4" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
+        <v>58</v>
+      </c>
+      <c r="B5">
+        <v>7</v>
+      </c>
+      <c r="C5" t="s">
+        <v>89</v>
+      </c>
+      <c r="E5" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
+        <v>92</v>
+      </c>
+      <c r="B6">
+        <f>SUBTOTAL(109,TTableTotalsShapes[n])</f>
+        <v>16</v>
+      </c>
+      <c r="C6">
+        <f>SUBTOTAL(103,TTableTotalsShapes[m])</f>
+        <v>4</v>
+      </c>
+      <c r="E6" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="E7" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="E8" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="12" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A12" t="s">
+        <v>91</v>
+      </c>
+      <c r="B12">
+        <f>SUM(B2:B5)</f>
+        <v>16</v>
+      </c>
+      <c r="C12">
+        <f>SUM(TTableTotalsShapes[n])</f>
+        <v>16</v>
+      </c>
+      <c r="D12">
+        <f>B5</f>
+        <v>7</v>
+      </c>
+    </row>
+  </sheetData>
+  <conditionalFormatting sqref="A2:C9">
+    <cfRule type="cellIs" priority="1" stopIfTrue="1" operator="greaterThan">
+      <formula>100</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B6:B9">
+    <cfRule type="cellIs" priority="2" stopIfTrue="1" operator="greaterThan">
+      <formula>200</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A6:C9">
+    <cfRule type="cellIs" priority="3" stopIfTrue="1" operator="greaterThan">
+      <formula>300</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="D9:E9 A6:C6">
+    <cfRule type="cellIs" priority="4" stopIfTrue="1" operator="greaterThan">
+      <formula>400</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A1:C9">
+    <cfRule type="cellIs" priority="5" stopIfTrue="1" operator="greaterThan">
+      <formula>500</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A6:C6">
+    <cfRule type="expression" priority="6" stopIfTrue="1">
+      <formula>$B6&gt;0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <dataValidations count="3">
+    <dataValidation type="textLength" operator="lessThanOrEqual" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="A2:A5 A6:A9" xr:uid="{F8DCDF36-F403-4E64-BC29-6AFE86F71E1A}">
+      <formula1>9</formula1>
+    </dataValidation>
+    <dataValidation type="whole" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="B1:B5 B6:B9" xr:uid="{D4402545-997E-49EF-829A-BAD2F126DE01}">
+      <formula1>0</formula1>
+      <formula2>99</formula2>
+    </dataValidation>
+    <dataValidation type="textLength" operator="lessThanOrEqual" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="C6:C9" xr:uid="{E74E7471-AA13-4E76-925A-9F5BFFCA93BC}">
+      <formula1>20</formula1>
+    </dataValidation>
+  </dataValidations>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <tableParts count="1">
+    <tablePart r:id="rId1"/>
+  </tableParts>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet19.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2099BD67-A979-4204-AE1A-80A81CB110DD}">
+  <dimension ref="A1:A6"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetData>
+    <row r="1" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A1">
+        <f>SUM(Table!B2:B5)</f>
+        <v>16</v>
+      </c>
+    </row>
+    <row r="2" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A2" s="1">
+        <f>Table!B7</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A3">
+        <f>SUM(TableTotals!B2:B5)</f>
+        <v>16</v>
+      </c>
+    </row>
+    <row r="4" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A4">
+        <f>TableTotals!B6</f>
+        <v>16</v>
+      </c>
+    </row>
+    <row r="5" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A5">
+        <f>SUM(TableTotals!A1:C6)</f>
+        <v>106</v>
+      </c>
+    </row>
+    <row r="6" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A6" s="1">
+        <f>TableTotals!B8</f>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -3079,23 +4401,1243 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5D8AA33F-E5C4-496C-9917-A3E6FE507D90}">
-  <dimension ref="A1:C12"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FE5BD09C-5124-4E33-948F-CA94AEBBB957}">
+  <dimension ref="A1:E11"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>64</v>
       </c>
       <c r="B1" t="s">
+        <v>67</v>
+      </c>
+      <c r="C1" t="s">
+        <v>68</v>
+      </c>
+      <c r="E1" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>8</v>
+      </c>
+      <c r="B2">
+        <v>1</v>
+      </c>
+      <c r="C2" t="s">
+        <v>69</v>
+      </c>
+      <c r="E2" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>8</v>
+      </c>
+      <c r="B3">
+        <v>2</v>
+      </c>
+      <c r="C3" t="s">
+        <v>70</v>
+      </c>
+      <c r="E3" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
+        <v>65</v>
+      </c>
+      <c r="B4">
+        <v>1</v>
+      </c>
+      <c r="C4" t="s">
+        <v>71</v>
+      </c>
+      <c r="E4" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
+        <v>66</v>
+      </c>
+      <c r="B5">
+        <v>3</v>
+      </c>
+      <c r="C5" t="s">
+        <v>72</v>
+      </c>
+      <c r="E5" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="E6" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="E7" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="10" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A10" t="str">
+        <f>A5&amp;B5&amp;C5</f>
+        <v>z3c6</v>
+      </c>
+      <c r="E10">
+        <f>COUNTA(A2:A7)</f>
+        <v>4</v>
+      </c>
+    </row>
+    <row r="11" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A11">
+        <f>SUM(B2:B7)</f>
+        <v>7</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet20.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{55C8F2CB-76AA-4B29-9332-B0ECAAB9A6C9}">
+  <dimension ref="A1:E12"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetData>
+    <row r="1" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1" t="s">
+        <v>64</v>
+      </c>
+      <c r="B1" t="s">
+        <v>67</v>
+      </c>
+      <c r="C1" t="s">
+        <v>1</v>
+      </c>
+      <c r="E1" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>7</v>
+      </c>
+      <c r="B2">
+        <v>1</v>
+      </c>
+      <c r="C2" t="s">
+        <v>83</v>
+      </c>
+      <c r="E2" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>80</v>
+      </c>
+      <c r="B3">
+        <v>3</v>
+      </c>
+      <c r="C3" t="s">
+        <v>85</v>
+      </c>
+      <c r="E3" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
+        <v>68</v>
+      </c>
+      <c r="B4">
+        <v>5</v>
+      </c>
+      <c r="C4" t="s">
+        <v>87</v>
+      </c>
+      <c r="E4" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
+        <v>58</v>
+      </c>
+      <c r="B5">
+        <v>7</v>
+      </c>
+      <c r="C5" t="s">
+        <v>89</v>
+      </c>
+      <c r="E5" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="E6" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="E7" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="E8" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="12" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A12" t="s">
+        <v>91</v>
+      </c>
+      <c r="B12">
+        <f>SUM(B2:B5)</f>
+        <v>16</v>
+      </c>
+      <c r="C12">
+        <f>SUM(TTableInner[n])</f>
+        <v>16</v>
+      </c>
+      <c r="D12">
+        <f>B5</f>
+        <v>7</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <tableParts count="1">
+    <tablePart r:id="rId1"/>
+  </tableParts>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet21.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1ADDDC95-3859-411E-A634-662807EA337C}">
+  <dimension ref="A1:E12"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetData>
+    <row r="1" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1" t="s">
+        <v>64</v>
+      </c>
+      <c r="B1" t="s">
+        <v>67</v>
+      </c>
+      <c r="C1" t="s">
+        <v>1</v>
+      </c>
+      <c r="E1" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>7</v>
+      </c>
+      <c r="B2">
+        <v>1</v>
+      </c>
+      <c r="C2" t="s">
+        <v>83</v>
+      </c>
+      <c r="E2" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>80</v>
+      </c>
+      <c r="B3">
+        <v>3</v>
+      </c>
+      <c r="C3" t="s">
+        <v>85</v>
+      </c>
+      <c r="E3" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
+        <v>68</v>
+      </c>
+      <c r="B4">
+        <v>5</v>
+      </c>
+      <c r="C4" t="s">
+        <v>87</v>
+      </c>
+      <c r="E4" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
+        <v>58</v>
+      </c>
+      <c r="B5">
+        <v>7</v>
+      </c>
+      <c r="C5" t="s">
+        <v>89</v>
+      </c>
+      <c r="E5" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="E6" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="E7" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="E8" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="12" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A12" t="s">
+        <v>91</v>
+      </c>
+      <c r="B12">
+        <f>SUM(B2:B5)</f>
+        <v>16</v>
+      </c>
+      <c r="C12">
+        <f>SUM(TTableCell[n])</f>
+        <v>16</v>
+      </c>
+      <c r="D12">
+        <f>B5</f>
+        <v>7</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <tableParts count="1">
+    <tablePart r:id="rId1"/>
+  </tableParts>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet22.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A8261341-5135-433F-B853-68EF35F62F21}">
+  <dimension ref="A1:E12"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetData>
+    <row r="1" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1" t="s">
+        <v>64</v>
+      </c>
+      <c r="B1" t="s">
+        <v>67</v>
+      </c>
+      <c r="C1" t="s">
+        <v>1</v>
+      </c>
+      <c r="E1" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>7</v>
+      </c>
+      <c r="B2">
+        <v>1</v>
+      </c>
+      <c r="C2" t="s">
+        <v>83</v>
+      </c>
+      <c r="E2" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>80</v>
+      </c>
+      <c r="B3">
+        <v>3</v>
+      </c>
+      <c r="C3" t="s">
+        <v>85</v>
+      </c>
+      <c r="E3" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
+        <v>68</v>
+      </c>
+      <c r="B4">
+        <v>5</v>
+      </c>
+      <c r="C4" t="s">
+        <v>87</v>
+      </c>
+      <c r="E4" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
+        <v>58</v>
+      </c>
+      <c r="B5">
+        <v>7</v>
+      </c>
+      <c r="C5" t="s">
+        <v>89</v>
+      </c>
+      <c r="E5" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="E6" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="E7" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="E8" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="12" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A12" t="s">
+        <v>91</v>
+      </c>
+      <c r="B12">
+        <f>SUM(B2:B5)</f>
+        <v>16</v>
+      </c>
+      <c r="C12">
+        <f>SUM(TTableNoHeaderAsked[n])</f>
+        <v>16</v>
+      </c>
+      <c r="D12">
+        <f>B5</f>
+        <v>7</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <tableParts count="1">
+    <tablePart r:id="rId1"/>
+  </tableParts>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet23.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{19048001-00E9-4A5F-8E58-9FBEBB305B56}">
+  <dimension ref="A1:E12"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetData>
+    <row r="1" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1" t="s">
+        <v>64</v>
+      </c>
+      <c r="B1" t="s">
+        <v>67</v>
+      </c>
+      <c r="C1" t="s">
+        <v>1</v>
+      </c>
+      <c r="E1" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>7</v>
+      </c>
+      <c r="B2">
+        <v>1</v>
+      </c>
+      <c r="C2" t="s">
+        <v>83</v>
+      </c>
+      <c r="E2" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>80</v>
+      </c>
+      <c r="B3">
+        <v>3</v>
+      </c>
+      <c r="C3" t="s">
+        <v>85</v>
+      </c>
+      <c r="E3" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
+        <v>68</v>
+      </c>
+      <c r="B4">
+        <v>5</v>
+      </c>
+      <c r="C4" t="s">
+        <v>87</v>
+      </c>
+      <c r="E4" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
+        <v>58</v>
+      </c>
+      <c r="B5">
+        <v>7</v>
+      </c>
+      <c r="C5" t="s">
+        <v>89</v>
+      </c>
+      <c r="E5" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
+        <v>92</v>
+      </c>
+      <c r="B6">
+        <f>SUBTOTAL(109,TTableTotalsRow[n])</f>
+        <v>16</v>
+      </c>
+      <c r="C6">
+        <f>SUBTOTAL(103,TTableTotalsRow[m])</f>
+        <v>4</v>
+      </c>
+      <c r="E6" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="E7" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="E8" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="12" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A12" t="s">
+        <v>91</v>
+      </c>
+      <c r="B12">
+        <f>SUM(B2:B5)</f>
+        <v>16</v>
+      </c>
+      <c r="C12">
+        <f>SUM(TTableTotalsRow[n])</f>
+        <v>16</v>
+      </c>
+      <c r="D12">
+        <f>B5</f>
+        <v>7</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <tableParts count="1">
+    <tablePart r:id="rId1"/>
+  </tableParts>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet24.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{621C4BCE-9D2F-4754-A9B8-290604BF5DD8}">
+  <dimension ref="A1:F12"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetData>
+    <row r="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A1" t="s">
+        <v>64</v>
+      </c>
+      <c r="B1" t="s">
+        <v>67</v>
+      </c>
+      <c r="C1" t="s">
+        <v>1</v>
+      </c>
+      <c r="D1" t="s">
+        <v>93</v>
+      </c>
+      <c r="F1" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>7</v>
+      </c>
+      <c r="B2">
+        <v>1</v>
+      </c>
+      <c r="C2" t="s">
+        <v>83</v>
+      </c>
+      <c r="D2" t="str">
+        <f>TTableCalc[[#This Row],[k]]&amp;TTableCalc[[#This Row],[n]]</f>
+        <v>a1</v>
+      </c>
+      <c r="F2" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>80</v>
+      </c>
+      <c r="B3">
+        <v>3</v>
+      </c>
+      <c r="C3" t="s">
+        <v>85</v>
+      </c>
+      <c r="D3" t="str">
+        <f>TTableCalc[[#This Row],[k]]&amp;TTableCalc[[#This Row],[n]]</f>
+        <v>b3</v>
+      </c>
+      <c r="F3" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
+        <v>68</v>
+      </c>
+      <c r="B4">
+        <v>5</v>
+      </c>
+      <c r="C4" t="s">
+        <v>87</v>
+      </c>
+      <c r="D4" t="str">
+        <f>TTableCalc[[#This Row],[k]]&amp;TTableCalc[[#This Row],[n]]</f>
+        <v>c5</v>
+      </c>
+      <c r="F4" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
+        <v>58</v>
+      </c>
+      <c r="B5">
+        <v>7</v>
+      </c>
+      <c r="C5" t="s">
+        <v>89</v>
+      </c>
+      <c r="D5" t="str">
+        <f>TTableCalc[[#This Row],[k]]&amp;TTableCalc[[#This Row],[n]]</f>
+        <v>d7</v>
+      </c>
+      <c r="F5" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="F6" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="F7" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="F8" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A12" t="s">
+        <v>91</v>
+      </c>
+      <c r="B12">
+        <f>SUM(B2:B5)</f>
+        <v>16</v>
+      </c>
+      <c r="C12">
+        <f>SUM(TTableCalc[n])</f>
+        <v>16</v>
+      </c>
+      <c r="D12">
+        <f>B5</f>
+        <v>7</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <tableParts count="1">
+    <tablePart r:id="rId1"/>
+  </tableParts>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet25.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CCAEC188-4E05-4C20-9971-C6D97C4F83F0}">
+  <dimension ref="A1:E12"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetData>
+    <row r="1" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1" t="s">
+        <v>64</v>
+      </c>
+      <c r="B1" t="s">
+        <v>67</v>
+      </c>
+      <c r="C1" t="s">
+        <v>1</v>
+      </c>
+      <c r="E1" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>7</v>
+      </c>
+      <c r="B2">
+        <v>1</v>
+      </c>
+      <c r="C2" t="s">
+        <v>83</v>
+      </c>
+      <c r="E2" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>80</v>
+      </c>
+      <c r="B3">
+        <v>3</v>
+      </c>
+      <c r="C3" t="s">
+        <v>85</v>
+      </c>
+      <c r="E3" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
+        <v>68</v>
+      </c>
+      <c r="B4">
+        <v>5</v>
+      </c>
+      <c r="C4" t="s">
+        <v>87</v>
+      </c>
+      <c r="E4" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
+        <v>58</v>
+      </c>
+      <c r="B5">
+        <v>7</v>
+      </c>
+      <c r="C5" t="s">
+        <v>89</v>
+      </c>
+      <c r="E5" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+      <c r="E6" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="E7" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+      <c r="E8" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="12" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A12" t="s">
+        <v>91</v>
+      </c>
+      <c r="B12">
+        <f>SUM(B2:B5)</f>
+        <v>16</v>
+      </c>
+      <c r="C12">
+        <f>SUM(TTableHidden[n])</f>
+        <v>16</v>
+      </c>
+      <c r="D12">
+        <f>B5</f>
+        <v>7</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <tableParts count="1">
+    <tablePart r:id="rId1"/>
+  </tableParts>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet26.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8929FD23-E9C0-44FA-901B-F5FFE9C1E5CD}">
+  <dimension ref="A1:E12"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetData>
+    <row r="1" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1" t="s">
+        <v>64</v>
+      </c>
+      <c r="B1" t="s">
+        <v>67</v>
+      </c>
+      <c r="C1" t="s">
+        <v>1</v>
+      </c>
+      <c r="E1" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>7</v>
+      </c>
+      <c r="B2">
+        <v>1</v>
+      </c>
+      <c r="C2" t="s">
+        <v>83</v>
+      </c>
+      <c r="E2" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>80</v>
+      </c>
+      <c r="B3">
+        <v>3</v>
+      </c>
+      <c r="C3" t="s">
+        <v>85</v>
+      </c>
+      <c r="E3" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
+        <v>68</v>
+      </c>
+      <c r="B4">
+        <v>5</v>
+      </c>
+      <c r="C4" t="s">
+        <v>87</v>
+      </c>
+      <c r="E4" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
+        <v>58</v>
+      </c>
+      <c r="B5">
+        <v>7</v>
+      </c>
+      <c r="C5" t="s">
+        <v>89</v>
+      </c>
+      <c r="E5" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="E6" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="E7" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="E8" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="12" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A12" t="s">
+        <v>91</v>
+      </c>
+      <c r="B12">
+        <f>SUM(B2:B5)</f>
+        <v>16</v>
+      </c>
+      <c r="C12">
+        <f>SUM(TTableFiltered[n])</f>
+        <v>16</v>
+      </c>
+      <c r="D12">
+        <f>B5</f>
+        <v>7</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <tableParts count="1">
+    <tablePart r:id="rId1"/>
+  </tableParts>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet27.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D31F8075-6BBE-4527-A6A1-1ED807101A7B}">
+  <dimension ref="A1:E12"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetData>
+    <row r="1" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1" t="s">
+        <v>64</v>
+      </c>
+      <c r="B1" t="s">
+        <v>67</v>
+      </c>
+      <c r="C1" t="s">
+        <v>1</v>
+      </c>
+      <c r="E1" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>7</v>
+      </c>
+      <c r="B2">
+        <v>1</v>
+      </c>
+      <c r="C2" t="s">
+        <v>83</v>
+      </c>
+      <c r="E2" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>80</v>
+      </c>
+      <c r="B3">
+        <v>3</v>
+      </c>
+      <c r="C3" t="s">
+        <v>85</v>
+      </c>
+      <c r="E3" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
+        <v>68</v>
+      </c>
+      <c r="B4">
+        <v>5</v>
+      </c>
+      <c r="C4" t="s">
+        <v>87</v>
+      </c>
+      <c r="E4" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
+        <v>58</v>
+      </c>
+      <c r="B5">
+        <v>7</v>
+      </c>
+      <c r="C5" t="s">
+        <v>89</v>
+      </c>
+      <c r="E5" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+      <c r="E6" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+      <c r="E7" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+      <c r="E8" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="9" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A9" t="s">
+        <v>92</v>
+      </c>
+      <c r="B9">
+        <f>SUBTOTAL(109,TTableFilteredTotals[n])</f>
+        <v>16</v>
+      </c>
+      <c r="C9">
+        <f>SUBTOTAL(103,TTableFilteredTotals[m])</f>
+        <v>4</v>
+      </c>
+    </row>
+    <row r="12" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A12" t="s">
+        <v>91</v>
+      </c>
+      <c r="B12">
+        <f>SUM(B2:B8)</f>
+        <v>16</v>
+      </c>
+      <c r="C12">
+        <f>SUM(TTableFilteredTotals[n])</f>
+        <v>16</v>
+      </c>
+      <c r="D12">
+        <f>B5</f>
+        <v>7</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <tableParts count="1">
+    <tablePart r:id="rId1"/>
+  </tableParts>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet28.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F34D972E-1393-4B10-A763-BDD51DA87F5C}">
+  <dimension ref="A1:E12"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetData>
+    <row r="1" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="E1" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>7</v>
+      </c>
+      <c r="B2">
+        <v>1</v>
+      </c>
+      <c r="C2" t="s">
+        <v>83</v>
+      </c>
+      <c r="E2" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>80</v>
+      </c>
+      <c r="B3">
+        <v>3</v>
+      </c>
+      <c r="C3" t="s">
+        <v>85</v>
+      </c>
+      <c r="E3" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
+        <v>68</v>
+      </c>
+      <c r="B4">
+        <v>5</v>
+      </c>
+      <c r="C4" t="s">
+        <v>87</v>
+      </c>
+      <c r="E4" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
+        <v>58</v>
+      </c>
+      <c r="B5">
+        <v>7</v>
+      </c>
+      <c r="C5" t="s">
+        <v>89</v>
+      </c>
+      <c r="E5" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="E6" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="E7" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="E8" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="12" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A12" t="s">
+        <v>91</v>
+      </c>
+      <c r="B12">
+        <f>SUM(B2:B5)</f>
+        <v>16</v>
+      </c>
+      <c r="C12">
+        <f>SUM(TTableHeadless[n])</f>
+        <v>16</v>
+      </c>
+      <c r="D12">
+        <f>B5</f>
+        <v>7</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <tableParts count="1">
+    <tablePart r:id="rId1"/>
+  </tableParts>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet29.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E68DC191-0726-47E9-91FE-D7AFAB4A415E}">
+  <dimension ref="A1:B4"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetData>
+    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A1" t="s">
+        <v>64</v>
+      </c>
+      <c r="B1" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>7</v>
+      </c>
+      <c r="B2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>80</v>
+      </c>
+      <c r="B3">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
+        <v>68</v>
+      </c>
+      <c r="B4">
+        <v>4</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <tableParts count="1">
+    <tablePart r:id="rId1"/>
+  </tableParts>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5FA310DF-88BC-4E08-8C2C-5BFC14440F3C}">
+  <dimension ref="A1:C12"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetData>
+    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A1" t="s">
+        <v>64</v>
+      </c>
+      <c r="B1" t="s">
         <v>81</v>
       </c>
       <c r="C1" t="s">
         <v>82</v>
       </c>
     </row>
-    <row r="2" spans="1:3" ht="14" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:3" ht="14.1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>7</v>
       </c>
@@ -3107,7 +5649,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="3" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>80</v>
       </c>
@@ -3119,7 +5661,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="4" spans="1:3" ht="16" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:3" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="21" t="s">
         <v>68</v>
       </c>
@@ -3131,7 +5673,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="5" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:3" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>58</v>
       </c>
@@ -3143,10 +5685,10 @@
         <v>80</v>
       </c>
     </row>
-    <row r="6" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="7" spans="1:3" ht="19" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="8" spans="1:3" ht="20" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="12" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="7" spans="1:3" ht="18.95" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="8" spans="1:3" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="12" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A12">
         <f>C3</f>
         <v>40</v>
@@ -3159,36 +5701,93 @@
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="1">
-    <dataValidation type="whole" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="C3" xr:uid="{C3ABF78D-6088-4DE9-B382-7DDE6001599B}">
+    <dataValidation type="whole" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="C3" xr:uid="{A8FF5C0C-8A2F-4118-ABBF-5F76A763F4FF}">
       <formula1>1</formula1>
       <formula2>9</formula2>
     </dataValidation>
   </dataValidations>
   <hyperlinks>
-    <hyperlink ref="A4" r:id="rId1" display="https://example.com/kept" xr:uid="{95178EC2-7777-45F5-BDE5-F29BD94EA434}"/>
+    <hyperlink ref="A4" r:id="rId1" display="https://example.com/kept" xr:uid="{C528E9BB-1E7C-48BD-B63F-F586D9D6D461}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <legacyDrawing r:id="rId2"/>
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B59E8BFB-30FF-41A5-9C70-F48B65D11040}">
-  <dimension ref="A1:C5"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+<file path=xl/worksheets/sheet30.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6FFBDB71-BE47-4C58-8C5F-F86499502BD2}">
+  <dimension ref="A1:B5"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>64</v>
       </c>
       <c r="B1" t="s">
         <v>67</v>
       </c>
+    </row>
+    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>7</v>
+      </c>
+      <c r="B2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>80</v>
+      </c>
+      <c r="B3">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
+        <v>68</v>
+      </c>
+      <c r="B4">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
+        <v>66</v>
+      </c>
+      <c r="B5">
+        <f>SUM(B1:B4)</f>
+        <v>7</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <tableParts count="1">
+    <tablePart r:id="rId1"/>
+  </tableParts>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet31.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A489178C-E911-4737-ADEF-1D356D900568}">
+  <dimension ref="A1:E12"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetData>
+    <row r="1" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1" t="s">
+        <v>64</v>
+      </c>
+      <c r="B1" t="s">
+        <v>67</v>
+      </c>
       <c r="C1" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="E1" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>7</v>
       </c>
@@ -3198,19 +5797,557 @@
       <c r="C2" t="s">
         <v>83</v>
       </c>
-    </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="E2" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>80</v>
       </c>
       <c r="B3">
+        <v>3</v>
+      </c>
+      <c r="C3" t="s">
+        <v>85</v>
+      </c>
+      <c r="E3" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
+        <v>68</v>
+      </c>
+      <c r="B4">
+        <v>5</v>
+      </c>
+      <c r="C4" t="s">
+        <v>87</v>
+      </c>
+      <c r="E4" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
+        <v>58</v>
+      </c>
+      <c r="B5">
+        <v>7</v>
+      </c>
+      <c r="C5" t="s">
+        <v>89</v>
+      </c>
+      <c r="E5" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="E6" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="E7" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="E8" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="12" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A12" t="s">
+        <v>91</v>
+      </c>
+      <c r="B12">
+        <f>SUM(B2:B5)</f>
+        <v>16</v>
+      </c>
+      <c r="C12">
+        <f>SUM(TTableSorted[n])</f>
+        <v>16</v>
+      </c>
+      <c r="D12">
+        <f>B5</f>
+        <v>7</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <tableParts count="1">
+    <tablePart r:id="rId1"/>
+  </tableParts>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet32.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F96F4A94-3ED3-4672-AFB3-CD7B18D0953D}">
+  <dimension ref="A1:E12"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetData>
+    <row r="1" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1" t="s">
+        <v>64</v>
+      </c>
+      <c r="B1" t="s">
+        <v>67</v>
+      </c>
+      <c r="C1" t="s">
+        <v>1</v>
+      </c>
+      <c r="E1" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>7</v>
+      </c>
+      <c r="B2">
+        <v>1</v>
+      </c>
+      <c r="C2" t="s">
+        <v>83</v>
+      </c>
+      <c r="E2" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>7</v>
+      </c>
+      <c r="B3">
         <v>2</v>
       </c>
       <c r="C3" t="s">
         <v>84</v>
       </c>
-    </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="E3" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
+        <v>80</v>
+      </c>
+      <c r="B4">
+        <v>3</v>
+      </c>
+      <c r="C4" t="s">
+        <v>85</v>
+      </c>
+      <c r="E4" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
+        <v>7</v>
+      </c>
+      <c r="B5">
+        <v>4</v>
+      </c>
+      <c r="C5" t="s">
+        <v>86</v>
+      </c>
+      <c r="E5" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
+        <v>68</v>
+      </c>
+      <c r="B6">
+        <v>5</v>
+      </c>
+      <c r="C6" t="s">
+        <v>87</v>
+      </c>
+      <c r="E6" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A7" t="s">
+        <v>80</v>
+      </c>
+      <c r="B7">
+        <v>6</v>
+      </c>
+      <c r="C7" t="s">
+        <v>88</v>
+      </c>
+      <c r="E7" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A8" t="s">
+        <v>58</v>
+      </c>
+      <c r="B8">
+        <v>7</v>
+      </c>
+      <c r="C8" t="s">
+        <v>89</v>
+      </c>
+      <c r="E8" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="12" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A12" t="s">
+        <v>91</v>
+      </c>
+      <c r="B12">
+        <f>SUM(B2:B8)</f>
+        <v>28</v>
+      </c>
+      <c r="C12">
+        <f>SUM(TTableUnique[n])</f>
+        <v>28</v>
+      </c>
+      <c r="D12">
+        <f>B5</f>
+        <v>4</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <tableParts count="1">
+    <tablePart r:id="rId1"/>
+  </tableParts>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet33.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BC8110F3-0299-4E9F-9B5E-4A190DAB461B}">
+  <dimension ref="A1:E12"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetData>
+    <row r="1" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1" t="s">
+        <v>64</v>
+      </c>
+      <c r="B1" t="s">
+        <v>67</v>
+      </c>
+      <c r="C1" t="s">
+        <v>1</v>
+      </c>
+      <c r="E1" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>7</v>
+      </c>
+      <c r="B2">
+        <v>1</v>
+      </c>
+      <c r="C2" t="s">
+        <v>83</v>
+      </c>
+      <c r="E2" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>7</v>
+      </c>
+      <c r="B3">
+        <v>2</v>
+      </c>
+      <c r="C3" t="s">
+        <v>84</v>
+      </c>
+      <c r="E3" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
+        <v>80</v>
+      </c>
+      <c r="B4">
+        <v>3</v>
+      </c>
+      <c r="C4" t="s">
+        <v>85</v>
+      </c>
+      <c r="E4" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
+        <v>7</v>
+      </c>
+      <c r="B5">
+        <v>4</v>
+      </c>
+      <c r="C5" t="s">
+        <v>86</v>
+      </c>
+      <c r="E5" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
+        <v>68</v>
+      </c>
+      <c r="B6">
+        <v>5</v>
+      </c>
+      <c r="C6" t="s">
+        <v>87</v>
+      </c>
+      <c r="E6" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A7" t="s">
+        <v>80</v>
+      </c>
+      <c r="B7">
+        <v>6</v>
+      </c>
+      <c r="C7" t="s">
+        <v>88</v>
+      </c>
+      <c r="E7" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A8" t="s">
+        <v>58</v>
+      </c>
+      <c r="B8">
+        <v>7</v>
+      </c>
+      <c r="C8" t="s">
+        <v>89</v>
+      </c>
+      <c r="E8" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="12" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A12" t="s">
+        <v>91</v>
+      </c>
+      <c r="B12">
+        <f>SUM(B2:B8)</f>
+        <v>28</v>
+      </c>
+      <c r="C12">
+        <f>SUM(TTableWider[n])</f>
+        <v>28</v>
+      </c>
+      <c r="D12">
+        <f>B5</f>
+        <v>4</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <tableParts count="1">
+    <tablePart r:id="rId1"/>
+  </tableParts>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet34.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{98DF8267-EAC6-4C79-9955-418B2FE29095}">
+  <dimension ref="A1:E12"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetData>
+    <row r="1" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1" t="s">
+        <v>64</v>
+      </c>
+      <c r="B1" t="s">
+        <v>67</v>
+      </c>
+      <c r="C1" t="s">
+        <v>1</v>
+      </c>
+      <c r="E1" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>7</v>
+      </c>
+      <c r="B2">
+        <v>1</v>
+      </c>
+      <c r="C2" t="s">
+        <v>83</v>
+      </c>
+      <c r="E2" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>7</v>
+      </c>
+      <c r="B3">
+        <v>2</v>
+      </c>
+      <c r="C3" t="s">
+        <v>84</v>
+      </c>
+      <c r="E3" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
+        <v>80</v>
+      </c>
+      <c r="B4">
+        <v>3</v>
+      </c>
+      <c r="C4" t="s">
+        <v>85</v>
+      </c>
+      <c r="E4" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
+        <v>7</v>
+      </c>
+      <c r="B5">
+        <v>4</v>
+      </c>
+      <c r="C5" t="s">
+        <v>86</v>
+      </c>
+      <c r="E5" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
+        <v>68</v>
+      </c>
+      <c r="B6">
+        <v>5</v>
+      </c>
+      <c r="C6" t="s">
+        <v>87</v>
+      </c>
+      <c r="E6" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A7" t="s">
+        <v>80</v>
+      </c>
+      <c r="B7">
+        <v>6</v>
+      </c>
+      <c r="C7" t="s">
+        <v>88</v>
+      </c>
+      <c r="E7" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A8" t="s">
+        <v>58</v>
+      </c>
+      <c r="B8">
+        <v>7</v>
+      </c>
+      <c r="C8" t="s">
+        <v>89</v>
+      </c>
+      <c r="E8" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="12" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A12" t="s">
+        <v>91</v>
+      </c>
+      <c r="B12">
+        <f>SUM(B2:B8)</f>
+        <v>28</v>
+      </c>
+      <c r="C12">
+        <f>SUM(TTableLonger[n])</f>
+        <v>28</v>
+      </c>
+      <c r="D12">
+        <f>B5</f>
+        <v>4</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <tableParts count="1">
+    <tablePart r:id="rId1"/>
+  </tableParts>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{70BCEE2F-93CE-47B4-A25E-CA3E429A52E8}">
+  <dimension ref="A1:C5"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetData>
+    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A1" t="s">
+        <v>64</v>
+      </c>
+      <c r="B1" t="s">
+        <v>67</v>
+      </c>
+      <c r="C1" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>7</v>
+      </c>
+      <c r="B2">
+        <v>1</v>
+      </c>
+      <c r="C2" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>80</v>
+      </c>
+      <c r="B3">
+        <v>2</v>
+      </c>
+      <c r="C3" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>68</v>
       </c>
@@ -3218,10 +6355,10 @@
         <v>4</v>
       </c>
       <c r="C4" t="s">
-        <v>85</v>
-      </c>
-    </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.35">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>58</v>
       </c>
@@ -3229,7 +6366,7 @@
         <v>6</v>
       </c>
       <c r="C5" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
     </row>
   </sheetData>
@@ -3244,15 +6381,15 @@
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="3">
-    <dataValidation type="whole" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="D2:D7 C2:C5" xr:uid="{8F27BA96-4101-4B68-94D0-22F547FC8CE9}">
+    <dataValidation type="whole" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="D2:D7 C2:C5" xr:uid="{8EA28272-63DB-45E2-9718-DAC06FFE2301}">
       <formula1>0</formula1>
       <formula2>9</formula2>
     </dataValidation>
-    <dataValidation type="decimal" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="B5" xr:uid="{E29F5F56-525F-45F4-9F42-48CAF72983E4}">
+    <dataValidation type="decimal" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="B5" xr:uid="{8718DFA5-7D29-4504-9334-914E6A79DB30}">
       <formula1>0</formula1>
       <formula2>9</formula2>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="A9" xr:uid="{506CA20F-1D62-41CC-BC01-BD556FFDD81E}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="A9" xr:uid="{932DD029-01F5-40DB-9C91-F2636BF8FBE2}">
       <formula1>"x,y"</formula1>
     </dataValidation>
   </dataValidations>
@@ -3261,11 +6398,11 @@
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8E10E2AB-220C-4D6B-9F8D-3DEE5A4540E7}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A4723899-1521-45E5-8682-380ED7BBE9A1}">
   <dimension ref="A1:B3"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>7</v>
       </c>
@@ -3273,7 +6410,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>80</v>
       </c>
@@ -3281,7 +6418,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>68</v>
       </c>
@@ -3295,11 +6432,11 @@
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4ED88664-746B-424E-8C1A-51164E8A3D54}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4E0759A4-CF3B-459C-9399-6096068A9534}">
   <dimension ref="A1:B5"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>64</v>
       </c>
@@ -3307,7 +6444,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>7</v>
       </c>
@@ -3315,7 +6452,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="3" spans="1:2" hidden="1" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:2" hidden="1" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>80</v>
       </c>
@@ -3323,7 +6460,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>68</v>
       </c>
@@ -3331,18 +6468,18 @@
         <v>4</v>
       </c>
     </row>
-    <row r="5" spans="1:2" hidden="1" x14ac:dyDescent="0.35"/>
+    <row r="5" spans="1:2" hidden="1" x14ac:dyDescent="0.25"/>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{87EC43E0-1004-41F5-9E7A-C8F1D999233D}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FDDD2BC1-3DC4-41C3-B075-ED87C2A966E3}">
   <dimension ref="A1:C4"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>64</v>
       </c>
@@ -3350,7 +6487,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>7</v>
       </c>
@@ -3358,7 +6495,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>7</v>
       </c>
@@ -3367,7 +6504,7 @@
       </c>
       <c r="C3" s="22"/>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>80</v>
       </c>
@@ -3384,11 +6521,11 @@
 </file>
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8CC82CCD-2359-4F80-8EBD-5A7D1063729D}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7035BBBB-8D04-4337-A252-B41AA6A21285}">
   <dimension ref="A1:C4"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>64</v>
       </c>
@@ -3396,7 +6533,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>7</v>
       </c>
@@ -3408,7 +6545,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>7</v>
       </c>
@@ -3419,7 +6556,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>80</v>
       </c>
@@ -3433,11 +6570,11 @@
 </file>
 
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{53103A8E-EC67-4959-BC28-7597EC4C8F14}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BCC05E5B-5970-41E4-BD21-3B1314F87190}">
   <dimension ref="A1:C4"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>64</v>
       </c>
@@ -3445,7 +6582,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>7</v>
       </c>
@@ -3457,7 +6594,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>80</v>
       </c>
@@ -3465,7 +6602,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>68</v>
       </c>
